--- a/docs/xlsx/jobs-2026-10-05.xlsx
+++ b/docs/xlsx/jobs-2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="730">
   <si>
     <t>Title</t>
   </si>
@@ -40,18 +40,1953 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Area Fisheries Biologist - Fish and Wildlife Biologist 3 - Permanent - 2026-08060</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$5,642 - $7,592 per month</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-area-fisheries-biologist---fish-and-wildlife-biologist-3---permanent---2026-08060-olympia-washington/2322223570</t>
+  </si>
+  <si>
+    <t>Associate or Senior Biologist/Regulatory Specialist</t>
+  </si>
+  <si>
+    <t>Dokken Engineering</t>
+  </si>
+  <si>
+    <t>Folsom, CA</t>
+  </si>
+  <si>
+    <t>$75,000 - $130,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-associate-or-senior-biologistregulatory-specialist-folsom-california/3844177446</t>
+  </si>
+  <si>
+    <t>Backyard Habitat PCEF Project Specialist</t>
+  </si>
+  <si>
+    <t>Bird Alliance of Oregon</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$30.24 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-backyard-habitat-pcef-project-specialist-portland-oregon/8581043479</t>
+  </si>
+  <si>
+    <t>Botany Project Manager</t>
+  </si>
+  <si>
+    <t>San Diego State University Research Foundation Soil Ecology and Restoration Group (SERG)</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>$27.73 per hour</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-botany-project-manager-san-diego-california/2956158831</t>
+  </si>
+  <si>
+    <t>Clean Energy Advocate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>The target annual compensation for someone with 2-5 years of relevant experience is $41,750-$46,000.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-clean-energy-advocate-oakland-california/7291104692</t>
+  </si>
+  <si>
+    <t>Clean Water Advocate</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>The starting annual compensation range for this position is $41,750-$46,000 for a candidate with 2-5 years of experience.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-clean-water-advocate-washington-dc/2304068729</t>
+  </si>
+  <si>
+    <t>Climate Change Outreach Specialist (Community Outreach &amp; Environmental Education Specialist 3)</t>
+  </si>
+  <si>
+    <t>WA State Department of Ecology</t>
+  </si>
+  <si>
+    <t>Spokane, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$54,204 - $72,900 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-climate-change-outreach-specialist-community-outreach--environmental-education-specialist-3-spokane-washington/9301792800</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Cottonwood Gulch Expeditions</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>$45,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications-manager-albuquerque-new-mexico/8091326952</t>
+  </si>
+  <si>
+    <t>Elkhorn Slough Foundation</t>
+  </si>
+  <si>
+    <t>Royal Oaks, CA</t>
+  </si>
+  <si>
+    <t>$75,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications-manager-royal-oaks-california/5630647759</t>
+  </si>
+  <si>
+    <t>Conservation Technician</t>
+  </si>
+  <si>
+    <t>Five Rivers MetroParks</t>
+  </si>
+  <si>
+    <t>Germantown, OH</t>
+  </si>
+  <si>
+    <t>$16.26 per hour</t>
+  </si>
+  <si>
+    <t>restoration-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-technician-germantown-ohio/7819386964</t>
+  </si>
+  <si>
+    <t>Construction Project Manager - Division of Parks and Recreation</t>
+  </si>
+  <si>
+    <t>Kent Conservation District</t>
+  </si>
+  <si>
+    <t>Dover, DE</t>
+  </si>
+  <si>
+    <t>$68,102.01 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-construction-project-manager---division-of-parks-and-recreation-dover-delaware/9213972795</t>
+  </si>
+  <si>
+    <t>Croatan Vegetation Management Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>Conservation Corps North Carolina</t>
+  </si>
+  <si>
+    <t>Bahama, NC</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$650 per week</t>
+  </si>
+  <si>
+    <t>forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-croatan-vegetation-management-assistant-crew-leader-bahama-north-carolina/9090915983</t>
+  </si>
+  <si>
+    <t>Croatan Vegetation Management Crew Leader</t>
+  </si>
+  <si>
+    <t>$925 - $1,125 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-croatan-vegetation-management-crew-leader-bahama-north-carolina/1840044401</t>
+  </si>
+  <si>
+    <t>Croatan Vegetation Management Crew Member</t>
+  </si>
+  <si>
+    <t>$600 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-croatan-vegetation-management-crew-member-bahama-north-carolina/9323765811</t>
+  </si>
+  <si>
+    <t>Cultural Resources Emergency Management Technician(NPS, RORI)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Richmond, CA</t>
+  </si>
+  <si>
+    <t>$36.97 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-cultural-resources-emergency-management-techniciannps-rori-richmond-california/6193696006</t>
+  </si>
+  <si>
+    <t>Director of Restoration</t>
+  </si>
+  <si>
+    <t>Anne Arundel Watershed Stewards Academy</t>
+  </si>
+  <si>
+    <t>Crownsville, MD</t>
+  </si>
+  <si>
+    <t>$75,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-restoration-crownsville-maryland/2676058550</t>
+  </si>
+  <si>
+    <t>District Forester (Sonora Forestry District)</t>
+  </si>
+  <si>
+    <t>Sierra Pacific Industries</t>
+  </si>
+  <si>
+    <t>Sonora, CA</t>
+  </si>
+  <si>
+    <t>$70,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-forester-sonora-forestry-district-sonora-california/8904403110</t>
+  </si>
+  <si>
+    <t>Education Coordinator</t>
+  </si>
+  <si>
+    <t>Wildlife Sanctuary of Northwest Florida</t>
+  </si>
+  <si>
+    <t>Pensacola, FL</t>
+  </si>
+  <si>
+    <t>$40,000 - $50,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-coordinator-pensacola-florida/9614348967</t>
+  </si>
+  <si>
+    <t>Environmental Campaigner</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Miami, FL</t>
+  </si>
+  <si>
+    <t>Pay and benefits are prorated for the length of your campaign position. The target annual compensation for this position is $40,000 (but compensation may range between $40,000 and $44,450 depending on location and start date).</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaigner-miami-florida/4330835473</t>
+  </si>
+  <si>
+    <t>Charleston, SC</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaigner-charleston-south-carolina/8462244166</t>
+  </si>
+  <si>
+    <t>Nashville, TN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaigner-nashville-tennessee/3744738424</t>
+  </si>
+  <si>
+    <t>Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaigner-phoenix-arizona/2789535052</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaigner-denver-colorado/6637448589</t>
+  </si>
+  <si>
+    <t>Environmental Engineer</t>
+  </si>
+  <si>
+    <t>Environmental Integrity Project</t>
+  </si>
+  <si>
+    <t>$105,000 - $132,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-engineer-washington-dc/2743670115</t>
+  </si>
+  <si>
+    <t>Environmental State Director, Wyoming</t>
+  </si>
+  <si>
+    <t>Cheyenne, WY</t>
+  </si>
+  <si>
+    <t>The starting annual compensation range for someone with 4-8 years of relevant experience is $43,500-$60,000.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-state-director-wyoming-cheyenne-wyoming/7948347579</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Tar River Land Conservancy</t>
+  </si>
+  <si>
+    <t>Louisburg, NC</t>
+  </si>
+  <si>
+    <t>$105,000 - $120,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-louisburg-north-carolina/2141405333</t>
+  </si>
+  <si>
+    <t>Fish Hatchery Specialist 3 - Naselle River Hatchery - Permanent - 2026-07274</t>
+  </si>
+  <si>
+    <t>Naselle, WA</t>
+  </si>
+  <si>
+    <t>$4,633 - $6,229 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-hatchery-specialist-3---naselle-river-hatchery---permanent---2026-07274-naselle-washington/5606286779</t>
+  </si>
+  <si>
+    <t>Forestry Project Manager</t>
+  </si>
+  <si>
+    <t>Bosland Growth</t>
+  </si>
+  <si>
+    <t>Morgantown, WV</t>
+  </si>
+  <si>
+    <t>$75,000 - $105,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-project-manager-morgantown-west-virginia/9985947256</t>
+  </si>
+  <si>
+    <t>Habitat Program Manager</t>
+  </si>
+  <si>
+    <t>Arizona Game and Fish Department</t>
+  </si>
+  <si>
+    <t>Kingmas, AZ</t>
+  </si>
+  <si>
+    <t>$60,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-habitat-program-manager-kingmas-arizona/5187186807</t>
+  </si>
+  <si>
+    <t>Helene Recovery Vegetation Management Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>Old Fort, NC</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-helene-recovery-vegetation-management-assistant-crew-leader-old-fort-north-carolina/8175289864</t>
+  </si>
+  <si>
+    <t>Helene Recovery Vegetation Management Crew Leader</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-helene-recovery-vegetation-management-crew-leader-old-fort-north-carolina/6478008842</t>
+  </si>
+  <si>
+    <t>Hunter Education Systems Coordinator</t>
+  </si>
+  <si>
+    <t>Wyoming Game &amp; Fish</t>
+  </si>
+  <si>
+    <t>$6,087.47 - $6,763.47 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hunter-education-systems-coordinator-cheyenne-wyoming/9696315849</t>
+  </si>
+  <si>
+    <t>Invasive Plant Strike Team Crew</t>
+  </si>
+  <si>
+    <t>Tucson Bird Alliance</t>
+  </si>
+  <si>
+    <t>Tucson, AZ</t>
+  </si>
+  <si>
+    <t>$21.78-$23.58 or $22.03-$24.09 if certified applicator</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-invasive-plant-strike-team-crew-tucson-arizona/2955562518</t>
+  </si>
+  <si>
+    <t>MT Science Integration Specialist</t>
+  </si>
+  <si>
+    <t>Northern Great Plains Joint Venture</t>
+  </si>
+  <si>
+    <t>Billings, MT, Remote</t>
+  </si>
+  <si>
+    <t>$60,000 - $63,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-mt-science-integration-specialist-billings-mt-remote/7194205045</t>
+  </si>
+  <si>
+    <t>Natural Resource Stewardship Technician</t>
+  </si>
+  <si>
+    <t>Missouri State Parks</t>
+  </si>
+  <si>
+    <t>Cassville, MO</t>
+  </si>
+  <si>
+    <t>$15.65 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resource-stewardship-technician-cassville-missouri/2271089131</t>
+  </si>
+  <si>
+    <t>Program Officer, Outreach and Education</t>
+  </si>
+  <si>
+    <t>Chesapeake Bay Trust</t>
+  </si>
+  <si>
+    <t>Annapolis, MD</t>
+  </si>
+  <si>
+    <t>$64,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-officer-outreach-and-education-annapolis-md-maryland/1437952443</t>
+  </si>
+  <si>
+    <t>Restoration Coordinator</t>
+  </si>
+  <si>
+    <t>James River Association</t>
+  </si>
+  <si>
+    <t>Scottsville, VA</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-coordinator-scottsville-virginia/5030103272</t>
+  </si>
+  <si>
+    <t>SCI Seasonal Invasive Technician</t>
+  </si>
+  <si>
+    <t>$24.65 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sci-seasonal-invasive-technician-san-diego-california/6001667623</t>
+  </si>
+  <si>
+    <t>SCI Seasonal Restoration Technician</t>
+  </si>
+  <si>
+    <t>$23.31 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sci-seasonal-restoration-technician-san-diego-california/5552837991</t>
+  </si>
+  <si>
+    <t>State Parks Mountains Trail Crew Leader</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-parks-mountains-trail-crew-leader-old-fort-north-carolina/4791890073</t>
+  </si>
+  <si>
+    <t>Vegetation Management Program Director</t>
+  </si>
+  <si>
+    <t>EnviroSystems Management, Inc.</t>
+  </si>
+  <si>
+    <t>Flagstaff, AZ</t>
+  </si>
+  <si>
+    <t>$80,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vegetation-management-program-director-flagstaff-arizona/9895092114</t>
+  </si>
+  <si>
+    <t>Visitor and Community Engagement Specialist - AmeriCorps</t>
+  </si>
+  <si>
+    <t>Conservation Legacy</t>
+  </si>
+  <si>
+    <t>Ajo, AZ</t>
+  </si>
+  <si>
+    <t>$640 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-visitor-and-community-engagement-specialist---americorps-ajo-arizona/3348517965</t>
+  </si>
+  <si>
+    <t>Water Agency Environmental Specialist</t>
+  </si>
+  <si>
+    <t>County of Sonoma</t>
+  </si>
+  <si>
+    <t>Santa Rosa, CA</t>
+  </si>
+  <si>
+    <t>$96,007.52 - $116,711.75 per year</t>
+  </si>
+  <si>
+    <t>ecology-policy-and-law-wildlife-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-agency-environmental-specialist-santa-rosa-california/3917628633</t>
+  </si>
+  <si>
+    <t>Wildlife Area Technician - Natural Resource Technician 3 - Permanent - 2026-08065</t>
+  </si>
+  <si>
+    <t>Brewster, WA</t>
+  </si>
+  <si>
+    <t>$3,738 - $4,980 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-area-technician---natural-resource-technician-3---permanent---2026-08065-brewster-washington/6169736528</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>Dorchester Bay Economic Development Corporation</t>
+  </si>
+  <si>
+    <t>Dorchester, MA</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba2c66f6832d444ebbb532e869c4d6a6-administrative-coordinator-dorchester-bay-economic-development-corporation-dorchester</t>
+  </si>
+  <si>
+    <t>Administrative Manager</t>
+  </si>
+  <si>
+    <t>Southern Maine Workers' Center</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 22000.00 - 22000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Job Workplace, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/36af3a06d32a44af9e540a31c18979fb-administrative-manager-southern-maine-workers-center-portland</t>
+  </si>
+  <si>
+    <t>Administrative Secretary</t>
+  </si>
+  <si>
+    <t>South Coastal Counties Legal Services Inc.</t>
+  </si>
+  <si>
+    <t>New Bedford, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 54182.25 - 84921.75/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/239f0604e0014b3782f9ba2fbbdff85a-administrative-secretary-south-coastal-counties-legal-services-inc-new-bedford</t>
+  </si>
+  <si>
+    <t>Advocacy &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>Katal Center for Equity, Health, and Justice</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1485df776bae44adbc416fde8c801d64-advocacy-communications-manager-katal-center-for-equity-health-and-justice-kings-county</t>
+  </si>
+  <si>
+    <t>Advocacy Coordinator</t>
+  </si>
+  <si>
+    <t>Bike East Bay</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 33.70 - 35.14/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae5c932489e5487abfdc8cc9a4db554b-advocacy-coordinator-bike-east-bay-oakland</t>
+  </si>
+  <si>
+    <t>Assistant Director - Animalearn</t>
+  </si>
+  <si>
+    <t>American Anti-Vivisection Society</t>
+  </si>
+  <si>
+    <t>Jenkintown, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 45000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bcf0204ca86e4be0b267e2c07c1a7df7-assistant-director-animalearn-american-anti-vivisection-society-jenkintown</t>
+  </si>
+  <si>
+    <t>ASSOCIATE SUPERVISING ATTORNEY, REMOVAL DEFENSE PROJECT</t>
+  </si>
+  <si>
+    <t>Catholic Migration Services</t>
+  </si>
+  <si>
+    <t>USD 97880.62 - 117664.36/year</t>
+  </si>
+  <si>
+    <t>Community Development, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16fd8b1c1990418c892540fca545b006-associate-supervising-attorney-removal-defense-project-catholic-migration-services-kings-county</t>
+  </si>
+  <si>
+    <t>ASSOCIATE, FUNDRAISING</t>
+  </si>
+  <si>
+    <t>Human Rights Watch</t>
+  </si>
+  <si>
+    <t>Stockholm, Stockholm County, SE</t>
+  </si>
+  <si>
+    <t>SEK 350000.00 - 365000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee34938e8d1b4e8db9a38f7b7c38c514-associate-fundraising-human-rights-watch-stockholm</t>
+  </si>
+  <si>
+    <t>Bilingual Housing Case Manager</t>
+  </si>
+  <si>
+    <t>Violence Intervention Program, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 31.59 - 31.59/hour</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bdccc5c6170243dbae1de0b23bdc933e-bilingual-housing-case-manager-violence-intervention-program-inc-new-york</t>
+  </si>
+  <si>
+    <t>Business Training Manager - Waltham</t>
+  </si>
+  <si>
+    <t>More Than Words</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/a3b1a824ef7b44b9b864245e5684548c-business-training-manager-waltham-more-than-words-waltham</t>
+  </si>
+  <si>
+    <t>Campaign Coordinator</t>
+  </si>
+  <si>
+    <t>Friends of Blackwater</t>
+  </si>
+  <si>
+    <t>Thomas, West Virginia</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Education, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dcf58769c68a4e529cbb7d1ea225b1af-campaign-coordinator-friends-of-blackwater-thomas</t>
+  </si>
+  <si>
+    <t>Campaign Fundraising Manager - Light the Night - Palm Beach</t>
+  </si>
+  <si>
+    <t>Blood Cancer United, formerly The Leukemia &amp; Lymphoma Society</t>
+  </si>
+  <si>
+    <t>Remote (Palm Beach, Florida)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9817b51b578b4c98b13db1263cd51ebc-campaign-fundraising-manager-light-the-night-palm-beach-blood-cancer-united-formerly-the-leukemia-lymphoma-society-palm-beach</t>
+  </si>
+  <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Barrio Logan College Institute (BLCI)</t>
+  </si>
+  <si>
+    <t>San Diego, California</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eaf59d87c6394a678ba3ac188d43f9e6-chief-development-officer-barrio-logan-college-institute-blci-san-diego</t>
+  </si>
+  <si>
+    <t>Chief Finance and Administration Officer</t>
+  </si>
+  <si>
+    <t>New York Common Pantry</t>
+  </si>
+  <si>
+    <t>USD 210000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a9cc75cd1be4232837e3a7021b9b9a5-chief-finance-and-administration-officer-new-york-common-pantry-new-york</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>League of Conservation Voters</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 225000.00 - 285000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/2a9a7410438a4555868ed7484f81bc2d-chief-operating-officer-league-of-conservation-voters-washington</t>
+  </si>
+  <si>
+    <t>Richmond Volleyball Club</t>
+  </si>
+  <si>
+    <t>Henrico, Virginia</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d6eac602f0f48acbc0a8ed81b413d25-chief-operating-officer-richmond-volleyball-club-henrico</t>
+  </si>
+  <si>
+    <t>Chief Operation Officer</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a64c6d2ddbd4e46a6bdd9d6970bbabd-chief-operation-officer-dorchester-bay-economic-development-corporation-dorchester</t>
+  </si>
+  <si>
+    <t>Chief Program &amp; Strategy Officer</t>
+  </si>
+  <si>
+    <t>USD 220000.00 - 250000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e42d30b38d084a6ebebcba952e10823f-chief-program-strategy-officer-new-york-common-pantry-new-york</t>
+  </si>
+  <si>
+    <t>Clinical Social Worker- Geriatric Mental Health Clinic</t>
+  </si>
+  <si>
+    <t>Jewish Association Serving the Aging</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 70040.00 - 73130.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30ad6de12bb14104bd4bf7bbc569ad45-clinical-social-worker-geriatric-mental-health-clinic-jewish-association-serving-the-aging-bronx</t>
+  </si>
+  <si>
+    <t>College and Career Advisor</t>
+  </si>
+  <si>
+    <t>Comprehensive Youth Development</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f98a9ae4ffd43979a60b0554ae7ead3-college-and-career-advisor-comprehensive-youth-development-new-york</t>
+  </si>
+  <si>
+    <t>College Counselor</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/178a92f480a34e4da466c79d81af24bb-college-counselor-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Communications &amp; Policy Manager</t>
+  </si>
+  <si>
+    <t>Build Up Justice NYC (previously Brooklyn Legal Services Corporation A)</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 87000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e048b458dfbb4928a5c7cf1f9f353188-communications-policy-manager-build-up-justice-nyc-previously-brooklyn-legal-services-corporation-a-brooklyn</t>
+  </si>
+  <si>
+    <t>Community Conservation Senior Manager</t>
+  </si>
+  <si>
+    <t>Panthera</t>
+  </si>
+  <si>
+    <t>Kafue, Lusaka Province, ZM</t>
+  </si>
+  <si>
+    <t>Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f8ef73a3a314bc7814aa5857753da76-community-conservation-senior-manager-panthera-kafue</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>USD 30.22 - 30.22/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92d7b76f5fef4aba9025aa5be33481ca-community-organizer-violence-intervention-program-inc-new-york</t>
+  </si>
+  <si>
+    <t>Community Programs &amp; Mental Health Support Coordinator</t>
+  </si>
+  <si>
+    <t>Huntington's Disease Youth Organization</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/929de844fa604f6db83945f389475d15-community-programs-mental-health-support-coordinator-huntingtons-disease-youth-organization-chicago</t>
+  </si>
+  <si>
+    <t>Contract Compliance and Impact Specialist or Analyst</t>
+  </si>
+  <si>
+    <t>Women's Opportunities Resource Center</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/685ee1127373455db4b00ea136f7af79-contract-compliance-and-impact-specialist-or-analyst-womens-opportunities-resource-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Corporate Partnerships Associate (Chicago, IL)</t>
+  </si>
+  <si>
+    <t>Rescuing Leftover Cuisine</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0be82d28b2644af88b47a4f89ae71db-corporate-partnerships-associate-chicago-il-rescuing-leftover-cuisine-chicago</t>
+  </si>
+  <si>
+    <t>Data Engineer, Data and Insights</t>
+  </si>
+  <si>
+    <t>UJA-Federation of New York</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0381e37ed79f49c885b967871de89b72-data-engineer-data-and-insights-uja-federation-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Deputy Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>New Jersey Citizen Action</t>
+  </si>
+  <si>
+    <t>Highland Park, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0669f3b3296842c4990b2a9c63016ccd-deputy-chief-financial-officer-new-jersey-citizen-action-highland-park</t>
+  </si>
+  <si>
+    <t>Deputy Director/Attorney, Compliance &amp; Training, Preserving Afforable Housing-Brooklyn</t>
+  </si>
+  <si>
+    <t>USD 116000.00 - 134000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ff01dfea7854d01a645d1645ede46b0-deputy-directorattorney-compliance-training-preserving-afforable-housing-brooklyn-build-up-justice-nyc-previously-brooklyn-legal-services-corporation-a-brooklyn</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>FriendshipWorks, Inc.</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c847750ae6540b894843195202528fb-development-coordinator-friendshipworks-inc-boston</t>
+  </si>
+  <si>
+    <t>Digital Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Farm Action</t>
+  </si>
+  <si>
+    <t>USD 59410.00 - 64045.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Consumer Protection, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0aaea425eea74d21a3aa83597b642fc1-digital-communications-coordinator-farm-action-mexico</t>
+  </si>
+  <si>
+    <t>Digital Skilling Program Coordinator</t>
+  </si>
+  <si>
+    <t>Hispanic Federation</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e2eb94cf5184dcfaa78d7f0611d0f3d-digital-skilling-program-coordinator-hispanic-federation-new-york</t>
+  </si>
+  <si>
+    <t>Director of Housing Stability Services</t>
+  </si>
+  <si>
+    <t>Arm In Arm</t>
+  </si>
+  <si>
+    <t>Hamilton Township, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd006b4af3634852a52116f7b0871f65-director-of-housing-stability-services-arm-in-arm-hamilton-township</t>
+  </si>
+  <si>
+    <t>Director of Marketing and Community Engagement</t>
+  </si>
+  <si>
+    <t>SPCA Westchester</t>
+  </si>
+  <si>
+    <t>Briarcliff Manor, New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1fce64627324b36a8f37037bed94756-director-of-marketing-and-community-engagement-spca-westchester-briarcliff-manor</t>
+  </si>
+  <si>
+    <t>Director, Human Resources Operations</t>
+  </si>
+  <si>
+    <t>Marlene Meyerson JCC Manhattan</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5450dfbd0e314ee09abbf39685b090bc-director-human-resources-operations-marlene-meyerson-jcc-manhattan-new-york</t>
+  </si>
+  <si>
+    <t>Domestic Violence Response Team Coordinator</t>
+  </si>
+  <si>
+    <t>Women Aware, Inc.</t>
+  </si>
+  <si>
+    <t>New Brunswick, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ba13a03982c4066aeb29379a0a26aab-domestic-violence-response-team-coordinator-women-aware-inc-new-brunswick</t>
+  </si>
+  <si>
+    <t>Engineering Expo and Events Coordinator</t>
+  </si>
+  <si>
+    <t>ACE Mentor Program of Greater New York, Inc.</t>
+  </si>
+  <si>
+    <t>USD 38000.00 - 42000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/563870b4ea8344bd92e5b08b1aa82528-engineering-expo-and-events-coordinator-ace-mentor-program-of-greater-new-york-inc-new-york</t>
+  </si>
+  <si>
+    <t>Events &amp; Volunteer Specialist</t>
+  </si>
+  <si>
+    <t>TreesCharlotte</t>
+  </si>
+  <si>
+    <t>Charlotte, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0326145921b8447cbe44caeca0a96501-events-volunteer-specialist-treescharlotte-charlotte</t>
+  </si>
+  <si>
+    <t>Events and Operations Associate - J-PAL North America</t>
+  </si>
+  <si>
+    <t>Abdul Latif Jameel Poverty Action Lab, MIT</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 63200.00 - 80050.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a958e4fd09bc451283eff48c1668b9e7-events-and-operations-associate-j-pal-north-america-abdul-latif-jameel-poverty-action-lab-mit-cambridge</t>
+  </si>
+  <si>
+    <t>Tupelo Press</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/70da3a974f60471289ff453a661713ad-executive-director-tupelo-press-north-adams</t>
+  </si>
+  <si>
+    <t>Executive Director at National Network of Abortion Funds</t>
+  </si>
+  <si>
+    <t>National Network of Abortion Funds</t>
+  </si>
+  <si>
+    <t>USD 243728.00 - 270810.00/year</t>
+  </si>
+  <si>
+    <t>Reproductive Health Rights, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/cabe7cadd1534b098abff86d41800452-executive-director-at-national-network-of-abortion-funds-national-network-of-abortion-funds-beaverton</t>
+  </si>
+  <si>
+    <t>Family Intervention Specialist - Memphis, TN</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Memphis, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/495a7fd43c124c45bf3d63b7ec1c2ba4-family-intervention-specialist-memphis-tn-youth-villages-memphis</t>
+  </si>
+  <si>
+    <t>Finance and Administration Manager</t>
+  </si>
+  <si>
+    <t>Artistree Community Arts Center</t>
+  </si>
+  <si>
+    <t>Pomfret, Vermont</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4957762c932543118077f18cb0ab7937-finance-and-administration-manager-artistree-community-arts-center-pomfret</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>Delaware Bankers Association and Delaware Financial Education Alliance</t>
+  </si>
+  <si>
+    <t>Dover, Delaware</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d3990a6639b4f6babc93319f27a1abb-finance-manager-delaware-bankers-association-and-delaware-financial-education-alliance-dover</t>
+  </si>
+  <si>
+    <t>Full Time Preschool Teacher</t>
+  </si>
+  <si>
+    <t>St. Paul's Littlest Angel Preschool</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 28.35/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b96bdcb70c16474d87bb5a4aded6a41c-full-time-preschool-teacher-st-pauls-littlest-angel-preschool-san-francisco</t>
+  </si>
+  <si>
+    <t>Grants Manager, Development and Communications</t>
+  </si>
+  <si>
+    <t>CAMBA</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7fede7f9c7a4aeabe0cfe43ab0876ce-grants-manager-development-and-communications-camba-kings-county</t>
+  </si>
+  <si>
+    <t>Health Benefits Trust Attorney</t>
+  </si>
+  <si>
+    <t>Massachusetts Municipal Association</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 168300.00 - 249900.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/205dfdab521e4a3caa4f58436289c021-health-benefits-trust-attorney-massachusetts-municipal-association-boston</t>
+  </si>
+  <si>
+    <t>Housing Resource Coordinator</t>
+  </si>
+  <si>
+    <t>Bethesda Cares, Inc.</t>
+  </si>
+  <si>
+    <t>Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e864a10af25249049dfe4d18fb687f8e-housing-resource-coordinator-bethesda-cares-inc-bethesda</t>
+  </si>
+  <si>
+    <t>Human Resources Administrator</t>
+  </si>
+  <si>
+    <t>David Lynch Foundation</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf30ba0e00a74e248a66d4a6e2b8a72b-human-resources-administrator-david-lynch-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Investigator (Spanish-Speaking)</t>
+  </si>
+  <si>
+    <t>The Bronx Defenders</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 70555.00 - 84660.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9bd740a2d2584d6c94d572d0c8cfca7f-investigator-spanish-speaking-the-bronx-defenders-bronx</t>
+  </si>
+  <si>
+    <t>Lead, Reviews (Early Literacy)</t>
+  </si>
+  <si>
+    <t>EdReports</t>
+  </si>
+  <si>
+    <t>USD 102824.00 - 139114.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/922ecebd16404624ad414758bb3f4120-lead-reviews-early-literacy-edreports-raleigh</t>
+  </si>
+  <si>
+    <t>Literacy Specialist</t>
+  </si>
+  <si>
+    <t>Literacy New Jersey</t>
+  </si>
+  <si>
+    <t>USD 50960.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9dbb96c1461f4bac99627212f8f05b7a-literacy-specialist-literacy-new-jersey-hamilton-township</t>
+  </si>
+  <si>
+    <t>Loan Administrator</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80c17dcdc82c40d9b4f450ff8c532d4d-loan-administrator-womens-opportunities-resource-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Mailroom Clerk Position</t>
+  </si>
+  <si>
+    <t>Appellate Advocates</t>
+  </si>
+  <si>
+    <t>USD 57589.16 - 71298.27/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a245a3423b5944a2affe09aa6fa56050-mailroom-clerk-position-appellate-advocates-new-york</t>
+  </si>
+  <si>
+    <t>Manager of Grants Compliance</t>
+  </si>
+  <si>
+    <t>Family Promise</t>
+  </si>
+  <si>
+    <t>USD 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/544251725bda49879e00ac487bb52d2b-manager-of-grants-compliance-family-promise-summit</t>
+  </si>
+  <si>
+    <t>Managing Attorney</t>
+  </si>
+  <si>
+    <t>The New York Immigration Coalition</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/128f6c5fc0a64035af6070e46b675d5a-managing-attorney-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Managing Director, Central Florida</t>
+  </si>
+  <si>
+    <t>Blessings in a Backpack</t>
+  </si>
+  <si>
+    <t>Orlando, Florida</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0502d25afa8645009d1b4998e44929f5-managing-director-central-florida-blessings-in-a-backpack-orlando</t>
+  </si>
+  <si>
+    <t>Maryland Coastal Fellowships</t>
+  </si>
+  <si>
+    <t>Coastal States Organization-Washington, DC</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a32d19b838964ce395e674e6fddfc5f4-maryland-coastal-fellowships-coastal-states-organization-washington-dc-annapolis</t>
+  </si>
+  <si>
+    <t>Nonprofit Administrative Assistant</t>
+  </si>
+  <si>
+    <t>The Samuel Lawrence Foundation</t>
+  </si>
+  <si>
+    <t>Solana Beach, California</t>
+  </si>
+  <si>
+    <t>USD 26.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f22f240b63b48c3b342752070ec7cef-nonprofit-administrative-assistant-the-samuel-lawrence-foundation-solana-beach</t>
+  </si>
+  <si>
+    <t>One-Year Prospect Development Analyst</t>
+  </si>
+  <si>
+    <t>Earthjustice</t>
+  </si>
+  <si>
+    <t>USD 75300.00 - 98400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1bb37f75c0c24d778806c6f5b1d95832-one-year-prospect-development-analyst-earthjustice-san-francisco</t>
+  </si>
+  <si>
+    <t>Operations Assistant</t>
+  </si>
+  <si>
+    <t>Project Knitwell</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afd682f154574b2fae1f106a2c9114e5-operations-assistant-project-knitwell-mclean</t>
+  </si>
+  <si>
+    <t>Operations Manager (Part-Time)</t>
+  </si>
+  <si>
+    <t>Ecclesia Ministries-common cathedral</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90ef037997c245e6a8acda22a8168e18-operations-manager-part-time-ecclesia-ministries-common-cathedral-boston</t>
+  </si>
+  <si>
+    <t>Operations Manager (People)</t>
+  </si>
+  <si>
+    <t>Lead Exposure Elimination Project</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3fdae7d14fd4102947cb1a710c341f2-operations-manager-people-lead-exposure-elimination-project-london</t>
+  </si>
+  <si>
+    <t>Organizer</t>
+  </si>
+  <si>
+    <t>32BJ SEIU</t>
+  </si>
+  <si>
+    <t>USD 68834.00 - 68834.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Civic Engagement, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c38c8bfea9b64d7d946174c5263c8968-organizer-32bj-seiu-new-york</t>
+  </si>
+  <si>
+    <t>Outreach Manager</t>
+  </si>
+  <si>
+    <t>Ariva</t>
+  </si>
+  <si>
+    <t>USD 66300.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Financial Literacy Personal Finance, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/edc040988cee48ed8e0666f008d1ac50-outreach-manager-ariva-bronx</t>
+  </si>
+  <si>
+    <t>Part Time Tenant Case Manager</t>
+  </si>
+  <si>
+    <t>Women's Community Revitalization Project</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/83fc4da8a8a64711810590945707d337-part-time-tenant-case-manager-womens-community-revitalization-project-philadelphia</t>
+  </si>
+  <si>
+    <t>Part-Time Executive Assistant</t>
+  </si>
+  <si>
+    <t>Mind-Builders Creative Arts Center</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 42.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6733354a200a4a6eb4f044a940315cf7-part-time-executive-assistant-mind-builders-creative-arts-center-bronx-county</t>
+  </si>
+  <si>
+    <t>Part-Time Licensed Mental Health Counselor</t>
+  </si>
+  <si>
+    <t>Arab American Association of New York</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da90e445b2f44d3fba7466d6a2859f60-part-time-licensed-mental-health-counselor-arab-american-association-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Part-Time Program Coordinator</t>
+  </si>
+  <si>
+    <t>New York Genealogical &amp; Biographical Society</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5b8ffbcf1da484bb01e9885933bf943-part-time-program-coordinator-new-york-genealogical-biographical-society-new-york</t>
+  </si>
+  <si>
+    <t>Part-Time Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 55.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf34a54174e4493f9f3154279d22cd2c-part-time-staff-attorney-arab-american-association-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>People &amp; Culture Manager, Benefits</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e3eccd10c884486942e8c898957bfe0-people-culture-manager-benefits-the-bronx-defenders-bronx</t>
+  </si>
+  <si>
+    <t>Program Assistant, American Statecraft Program</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/136e58b78dba467c89ff5450c1e94d48-program-assistant-american-statecraft-program-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
+    <t>Program Associate, Impact Purchasing &amp; Place-based Investing</t>
+  </si>
+  <si>
+    <t>Healthcare Anchor Network</t>
+  </si>
+  <si>
+    <t>USD 63045.00 - 69713.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b85215e1ba94c769001dec5829f30b6-program-associate-impact-purchasing-place-based-investing-healthcare-anchor-network-washington</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Boys &amp; Girls Clubs of Napa Valley</t>
+  </si>
+  <si>
+    <t>Napa, California</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e1eebe26a474415b35d09c9901ebd5b-program-director-boys-girls-clubs-of-napa-valley-napa</t>
+  </si>
+  <si>
+    <t>Program Manager - Tutoring Programs at Rikers Island</t>
+  </si>
+  <si>
+    <t>The Petey Greene Program</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb69e40c09494a83a78d861006520f26-program-manager-tutoring-programs-at-rikers-island-the-petey-greene-program-new-york</t>
+  </si>
+  <si>
+    <t>Programs Officer, Scholars Programs</t>
+  </si>
+  <si>
+    <t>SEEDS - Access Changes Everything</t>
+  </si>
+  <si>
+    <t>Newark, NJ</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f62425c60074df1b01bdd7517a573f1-programs-officer-scholars-programs-seeds-access-changes-everything-newark</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>The Allentown Parknership</t>
+  </si>
+  <si>
+    <t>Allentown, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f91aa1d2448419c8db489c0a09f346f-project-manager-the-allentown-parknership-allentown</t>
+  </si>
+  <si>
+    <t>Recruiting Specialist</t>
+  </si>
+  <si>
+    <t>The Salvation Army National Headquarters</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 56291.00 - 73106.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/41620065c1394d5981fbfdb1bbb12769-recruiting-specialist-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Recruitment Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05ac7d5a224246209b2acc510ada770d-recruitment-associate-lead-exposure-elimination-project-london</t>
+  </si>
+  <si>
+    <t>RED KETTLE PARTNERS DIRECTOR</t>
+  </si>
+  <si>
+    <t>USD 97038.00 - 126024.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df97126f5fc64c1f94d1cfb87e3bacba-red-kettle-partners-director-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>RentSelect Account Specialist</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5c073e10a3d4f6d907a5b0e41d73abe-rentselect-account-specialist-bethesda-cares-inc-bethesda</t>
+  </si>
+  <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>Roseland, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 86900.00 - 95800.00/year</t>
+  </si>
+  <si>
+    <t>Volunteering, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea5ebd7b5b244bd5a0bca2d377cc4395-senior-accountant-roseland</t>
+  </si>
+  <si>
+    <t>Senior Data Analyst</t>
+  </si>
+  <si>
+    <t>Homebase</t>
+  </si>
+  <si>
+    <t>USD 84500.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1626c6b1b2534d4292ea810ce61a0e9e-senior-data-analyst-homebase-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Director of Parenting Education, Training and Technical Assistance</t>
+  </si>
+  <si>
+    <t>Family Nurturing Center of MA</t>
+  </si>
+  <si>
+    <t>Dorchester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 98000.00 - 106000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/31b1ed8b5e6344249ad30ca03926df3e-senior-director-of-parenting-education-training-and-technical-assistance-family-nurturing-center-of-ma-dorchester</t>
+  </si>
+  <si>
+    <t>Senior Manager, Foundation Operations</t>
+  </si>
+  <si>
+    <t>Intentional Philanthropy</t>
+  </si>
+  <si>
+    <t>USD 73500.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/434b78f5526941ff962d5ccb7ccf9cd0-senior-manager-foundation-operations-intentional-philanthropy-bethesda</t>
+  </si>
+  <si>
     <t>Senior Marketing &amp; Automation Lead for Nonprofit / Social Impact Projects (Assistance Dogs)</t>
   </si>
   <si>
     <t>Pfotenpiloten Alliance for Assistance Dogs</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>EUR 25.00/hour</t>
   </si>
   <si>
@@ -59,6 +1994,216 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/1d86ab2b509847c59c6736cf355f7a52-senior-marketing-automation-lead-for-nonprofit-social-impact-projects-assistance-dogs-pfotenpiloten-alliance-for-assistance-dogs-frankfurt-am-main</t>
+  </si>
+  <si>
+    <t>Senior People Operations Manager</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b38844cece8468b868f464c94919fd3-senior-people-operations-manager-greenlight-america-washington</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0be86b17ec44088bc5df17be7e60e91-senior-staff-attorney-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Service Enriched Housing Super Hero</t>
+  </si>
+  <si>
+    <t>Community Housing Resource Partners, Inc.</t>
+  </si>
+  <si>
+    <t>Denton, Texas</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d517f7539aa840f0a290cfec3c5041d9-service-enriched-housing-super-hero-community-housing-resource-partners-inc-denton</t>
+  </si>
+  <si>
+    <t>Shelter and Interim-Housing Associate</t>
+  </si>
+  <si>
+    <t>Better Angels</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ee3a8b101dc40af8959935e5ed22501-shelter-and-interim-housing-associate-better-angels-los-angeles</t>
+  </si>
+  <si>
+    <t>Social Media &amp; Content Associate</t>
+  </si>
+  <si>
+    <t>Patients For Affordable Drugs</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0665bd7a80a848d9a8f506b3c17a6e94-social-media-content-associate-patients-for-affordable-drugs-washington</t>
+  </si>
+  <si>
+    <t>Solutions Consultant</t>
+  </si>
+  <si>
+    <t>Bitfocus</t>
+  </si>
+  <si>
+    <t>USD 49000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/a90a525fc6f84ff09e77946f07d4058c-solutions-consultant-bitfocus-las-vegas</t>
+  </si>
+  <si>
+    <t>Sr. Software Engineer</t>
+  </si>
+  <si>
+    <t>Unify America</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac790a01e75649468aceb3b9d7902767-sr-software-engineer-unify-america-chicago</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 109000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f351f797ce0a4dcfa03633258ba48e90-staff-attorney-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Group Representation - Preserving Affordable Housing Program-Brooklyn</t>
+  </si>
+  <si>
+    <t>USD 81600.00 - 103200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed1af86214d34924afb7025457db2a4f-staff-attorney-group-representation-preserving-affordable-housing-program-brooklyn-build-up-justice-nyc-previously-brooklyn-legal-services-corporation-a-brooklyn</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Preserving Affordable Housing Program-Brooklyn</t>
+  </si>
+  <si>
+    <t>USD 81600.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4eb32b18fc0440978bb6c0754973acd9-staff-attorney-preserving-affordable-housing-program-brooklyn-build-up-justice-nyc-previously-brooklyn-legal-services-corporation-a-brooklyn</t>
+  </si>
+  <si>
+    <t>Street Outreach Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca00dab425794640b6006338338d84fd-street-outreach-manager-bethesda-cares-inc-bethesda</t>
+  </si>
+  <si>
+    <t>Supervising Staff Attorney, Preserving Affordable Housing - Brooklyn</t>
+  </si>
+  <si>
+    <t>USD 101000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bde5e87bc1d145c9b7495ebcd4ca6a96-supervising-staff-attorney-preserving-affordable-housing-brooklyn-build-up-justice-nyc-previously-brooklyn-legal-services-corporation-a-brooklyn</t>
+  </si>
+  <si>
+    <t>Systems Change &amp; Policy Strategy Manager</t>
+  </si>
+  <si>
+    <t>Rebel Heart Therapy</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/8650e7ff06dc4963a92ac1d6d319d371-systems-change-policy-strategy-manager-rebel-heart-therapy-portland</t>
+  </si>
+  <si>
+    <t>Temporary Housing Attorney</t>
+  </si>
+  <si>
+    <t>Legal Aid Society of San Mateo County</t>
+  </si>
+  <si>
+    <t>Redwood City, California</t>
+  </si>
+  <si>
+    <t>USD 1655.00 - 2177.00/week</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4283e1aacb9b48a68c81ba565c6c8051-temporary-housing-attorney-legal-aid-society-of-san-mateo-county-redwood-city</t>
+  </si>
+  <si>
+    <t>Vice President of Digital Products</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d6571a8ddf5488e9ad134ded14b9ce0-vice-president-of-digital-products-marlene-meyerson-jcc-manhattan-new-york</t>
+  </si>
+  <si>
+    <t>VP, Finance and Accounting</t>
+  </si>
+  <si>
+    <t>Inclusiv</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec6aece6070649dd8dcda8a99e426e79-vp-finance-and-accounting-inclusiv-kings-county</t>
+  </si>
+  <si>
+    <t>Youth Employment Specialist</t>
+  </si>
+  <si>
+    <t>Bridges From School to Work Inc.</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e21b69fbc16d427e845a2e97c603fa1e-youth-employment-specialist-bridges-from-school-to-work-inc-chicago</t>
   </si>
 </sst>
 </file>
@@ -444,7 +2589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -483,8 +2628,1066 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" t="s">
+        <v>135</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29" t="s">
+        <v>145</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" t="s">
+        <v>148</v>
+      </c>
+      <c r="C30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" t="s">
+        <v>77</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>158</v>
+      </c>
+      <c r="B33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>160</v>
+      </c>
+      <c r="F33" t="s">
+        <v>161</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" t="s">
+        <v>165</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>166</v>
+      </c>
+      <c r="F34" t="s">
+        <v>167</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35" t="s">
+        <v>173</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>178</v>
+      </c>
+      <c r="F36" t="s">
+        <v>77</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" t="s">
+        <v>182</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>183</v>
+      </c>
+      <c r="F37" t="s">
+        <v>184</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" t="s">
+        <v>192</v>
+      </c>
+      <c r="F39" t="s">
+        <v>167</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>194</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" t="s">
+        <v>195</v>
+      </c>
+      <c r="F40" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>197</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" t="s">
+        <v>80</v>
+      </c>
+      <c r="F41" t="s">
+        <v>198</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" t="s">
+        <v>204</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>206</v>
+      </c>
+      <c r="B43" t="s">
+        <v>207</v>
+      </c>
+      <c r="C43" t="s">
+        <v>208</v>
+      </c>
+      <c r="D43" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" t="s">
+        <v>209</v>
+      </c>
+      <c r="F43" t="s">
+        <v>210</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>212</v>
+      </c>
+      <c r="B44" t="s">
+        <v>213</v>
+      </c>
+      <c r="C44" t="s">
+        <v>214</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>215</v>
+      </c>
+      <c r="F44" t="s">
+        <v>216</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s">
+        <v>219</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>220</v>
+      </c>
+      <c r="F45" t="s">
+        <v>151</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -540,7 +3743,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -581,31 +3784,2503 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>222</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>226</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>227</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+      <c r="E6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F7" t="s">
+        <v>259</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F8" t="s">
+        <v>264</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" t="s">
+        <v>274</v>
+      </c>
+      <c r="D10" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F10" t="s">
+        <v>276</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E11" t="s">
+        <v>281</v>
+      </c>
+      <c r="F11" t="s">
+        <v>276</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" t="s">
+        <v>286</v>
+      </c>
+      <c r="F12" t="s">
+        <v>287</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>289</v>
+      </c>
+      <c r="B13" t="s">
+        <v>290</v>
+      </c>
+      <c r="C13" t="s">
+        <v>291</v>
+      </c>
+      <c r="D13" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" t="s">
+        <v>292</v>
+      </c>
+      <c r="F13" t="s">
+        <v>293</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B14" t="s">
+        <v>296</v>
+      </c>
+      <c r="C14" t="s">
+        <v>297</v>
+      </c>
+      <c r="D14" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" t="s">
+        <v>298</v>
+      </c>
+      <c r="F14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" t="s">
+        <v>302</v>
+      </c>
+      <c r="C15" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E15" t="s">
+        <v>303</v>
+      </c>
+      <c r="F15" t="s">
+        <v>276</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>305</v>
+      </c>
+      <c r="B16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" t="s">
+        <v>225</v>
+      </c>
+      <c r="E16" t="s">
+        <v>308</v>
+      </c>
+      <c r="F16" t="s">
+        <v>276</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" t="s">
+        <v>310</v>
+      </c>
+      <c r="C17" t="s">
+        <v>311</v>
+      </c>
+      <c r="D17" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" t="s">
+        <v>312</v>
+      </c>
+      <c r="F17" t="s">
+        <v>313</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>315</v>
+      </c>
+      <c r="B18" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" t="s">
+        <v>224</v>
+      </c>
+      <c r="D18" t="s">
+        <v>225</v>
+      </c>
+      <c r="E18" t="s">
+        <v>316</v>
+      </c>
+      <c r="F18" t="s">
+        <v>227</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C19" t="s">
+        <v>274</v>
+      </c>
+      <c r="D19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" t="s">
+        <v>319</v>
+      </c>
+      <c r="F19" t="s">
+        <v>276</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>321</v>
+      </c>
+      <c r="B20" t="s">
+        <v>322</v>
+      </c>
+      <c r="C20" t="s">
+        <v>323</v>
+      </c>
+      <c r="D20" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" t="s">
+        <v>324</v>
+      </c>
+      <c r="F20" t="s">
+        <v>276</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>326</v>
+      </c>
+      <c r="B21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C21" t="s">
+        <v>274</v>
+      </c>
+      <c r="D21" t="s">
+        <v>225</v>
+      </c>
+      <c r="E21" t="s">
+        <v>328</v>
+      </c>
+      <c r="F21" t="s">
+        <v>329</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>331</v>
+      </c>
+      <c r="B22" t="s">
+        <v>332</v>
+      </c>
+      <c r="C22" t="s">
+        <v>333</v>
+      </c>
+      <c r="D22" t="s">
+        <v>225</v>
+      </c>
+      <c r="E22" t="s">
+        <v>334</v>
+      </c>
+      <c r="F22" t="s">
+        <v>335</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B23" t="s">
+        <v>338</v>
+      </c>
+      <c r="C23" t="s">
+        <v>339</v>
+      </c>
+      <c r="D23" t="s">
+        <v>225</v>
+      </c>
+      <c r="E23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F23" t="s">
+        <v>227</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>342</v>
+      </c>
+      <c r="B24" t="s">
+        <v>343</v>
+      </c>
+      <c r="C24" t="s">
+        <v>344</v>
+      </c>
+      <c r="D24" t="s">
+        <v>225</v>
+      </c>
+      <c r="E24" t="s">
+        <v>276</v>
+      </c>
+      <c r="F24" t="s">
+        <v>345</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>347</v>
+      </c>
+      <c r="B25" t="s">
+        <v>273</v>
+      </c>
+      <c r="C25" t="s">
+        <v>274</v>
+      </c>
+      <c r="D25" t="s">
+        <v>251</v>
+      </c>
+      <c r="E25" t="s">
+        <v>348</v>
+      </c>
+      <c r="F25" t="s">
+        <v>349</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>351</v>
+      </c>
+      <c r="B26" t="s">
+        <v>352</v>
+      </c>
+      <c r="C26" t="s">
+        <v>353</v>
+      </c>
+      <c r="D26" t="s">
+        <v>225</v>
+      </c>
+      <c r="E26" t="s">
+        <v>276</v>
+      </c>
+      <c r="F26" t="s">
+        <v>354</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>356</v>
+      </c>
+      <c r="B27" t="s">
+        <v>357</v>
+      </c>
+      <c r="C27" t="s">
+        <v>358</v>
+      </c>
+      <c r="D27" t="s">
+        <v>251</v>
+      </c>
+      <c r="E27" t="s">
+        <v>359</v>
+      </c>
+      <c r="F27" t="s">
+        <v>360</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>362</v>
+      </c>
+      <c r="B28" t="s">
+        <v>363</v>
+      </c>
+      <c r="C28" t="s">
+        <v>364</v>
+      </c>
+      <c r="D28" t="s">
+        <v>365</v>
+      </c>
+      <c r="E28" t="s">
+        <v>366</v>
+      </c>
+      <c r="F28" t="s">
+        <v>367</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>369</v>
+      </c>
+      <c r="B29" t="s">
+        <v>370</v>
+      </c>
+      <c r="C29" t="s">
+        <v>274</v>
+      </c>
+      <c r="D29" t="s">
+        <v>225</v>
+      </c>
+      <c r="E29" t="s">
+        <v>371</v>
+      </c>
+      <c r="F29" t="s">
+        <v>372</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>374</v>
+      </c>
+      <c r="B30" t="s">
+        <v>375</v>
+      </c>
+      <c r="C30" t="s">
+        <v>376</v>
+      </c>
+      <c r="D30" t="s">
+        <v>225</v>
+      </c>
+      <c r="E30" t="s">
+        <v>377</v>
+      </c>
+      <c r="F30" t="s">
+        <v>276</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>379</v>
+      </c>
+      <c r="B31" t="s">
+        <v>338</v>
+      </c>
+      <c r="C31" t="s">
+        <v>339</v>
+      </c>
+      <c r="D31" t="s">
+        <v>225</v>
+      </c>
+      <c r="E31" t="s">
+        <v>380</v>
+      </c>
+      <c r="F31" t="s">
+        <v>227</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>382</v>
+      </c>
+      <c r="B32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C32" t="s">
+        <v>384</v>
+      </c>
+      <c r="D32" t="s">
+        <v>225</v>
+      </c>
+      <c r="E32" t="s">
+        <v>385</v>
+      </c>
+      <c r="F32" t="s">
+        <v>386</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>388</v>
+      </c>
+      <c r="B33" t="s">
+        <v>389</v>
+      </c>
+      <c r="C33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D33" t="s">
+        <v>225</v>
+      </c>
+      <c r="E33" t="s">
+        <v>390</v>
+      </c>
+      <c r="F33" t="s">
+        <v>391</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>393</v>
+      </c>
+      <c r="B34" t="s">
+        <v>394</v>
+      </c>
+      <c r="C34" t="s">
+        <v>274</v>
+      </c>
+      <c r="D34" t="s">
+        <v>225</v>
+      </c>
+      <c r="E34" t="s">
+        <v>395</v>
+      </c>
+      <c r="F34" t="s">
+        <v>276</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>397</v>
+      </c>
+      <c r="B35" t="s">
+        <v>398</v>
+      </c>
+      <c r="C35" t="s">
+        <v>399</v>
+      </c>
+      <c r="D35" t="s">
+        <v>225</v>
+      </c>
+      <c r="E35" t="s">
+        <v>400</v>
+      </c>
+      <c r="F35" t="s">
+        <v>401</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>403</v>
+      </c>
+      <c r="B36" t="s">
+        <v>404</v>
+      </c>
+      <c r="C36" t="s">
+        <v>405</v>
+      </c>
+      <c r="D36" t="s">
+        <v>225</v>
+      </c>
+      <c r="E36" t="s">
+        <v>406</v>
+      </c>
+      <c r="F36" t="s">
+        <v>407</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>409</v>
+      </c>
+      <c r="B37" t="s">
+        <v>410</v>
+      </c>
+      <c r="C37" t="s">
+        <v>274</v>
+      </c>
+      <c r="D37" t="s">
+        <v>225</v>
+      </c>
+      <c r="E37" t="s">
+        <v>411</v>
+      </c>
+      <c r="F37" t="s">
+        <v>276</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>413</v>
+      </c>
+      <c r="B38" t="s">
+        <v>414</v>
+      </c>
+      <c r="C38" t="s">
+        <v>415</v>
+      </c>
+      <c r="D38" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" t="s">
+        <v>416</v>
+      </c>
+      <c r="F38" t="s">
+        <v>417</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>419</v>
+      </c>
+      <c r="B39" t="s">
+        <v>420</v>
+      </c>
+      <c r="C39" t="s">
+        <v>274</v>
+      </c>
+      <c r="D39" t="s">
+        <v>225</v>
+      </c>
+      <c r="E39" t="s">
+        <v>421</v>
+      </c>
+      <c r="F39" t="s">
+        <v>422</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>424</v>
+      </c>
+      <c r="B40" t="s">
+        <v>425</v>
+      </c>
+      <c r="C40" t="s">
+        <v>426</v>
+      </c>
+      <c r="D40" t="s">
+        <v>225</v>
+      </c>
+      <c r="E40" t="s">
+        <v>427</v>
+      </c>
+      <c r="F40" t="s">
+        <v>428</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>430</v>
+      </c>
+      <c r="B41" t="s">
+        <v>431</v>
+      </c>
+      <c r="C41" t="s">
+        <v>432</v>
+      </c>
+      <c r="D41" t="s">
+        <v>225</v>
+      </c>
+      <c r="E41" t="s">
+        <v>433</v>
+      </c>
+      <c r="F41" t="s">
+        <v>434</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>436</v>
+      </c>
+      <c r="C42" t="s">
+        <v>353</v>
+      </c>
+      <c r="D42" t="s">
+        <v>225</v>
+      </c>
+      <c r="E42" t="s">
+        <v>437</v>
+      </c>
+      <c r="F42" t="s">
+        <v>438</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>440</v>
+      </c>
+      <c r="B43" t="s">
+        <v>441</v>
+      </c>
+      <c r="C43" t="s">
+        <v>353</v>
+      </c>
+      <c r="D43" t="s">
+        <v>225</v>
+      </c>
+      <c r="E43" t="s">
+        <v>442</v>
+      </c>
+      <c r="F43" t="s">
+        <v>443</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>445</v>
+      </c>
+      <c r="B44" t="s">
+        <v>446</v>
+      </c>
+      <c r="C44" t="s">
+        <v>447</v>
+      </c>
+      <c r="D44" t="s">
+        <v>225</v>
+      </c>
+      <c r="E44" t="s">
+        <v>448</v>
+      </c>
+      <c r="F44" t="s">
+        <v>449</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>451</v>
+      </c>
+      <c r="B45" t="s">
+        <v>452</v>
+      </c>
+      <c r="C45" t="s">
+        <v>453</v>
+      </c>
+      <c r="D45" t="s">
+        <v>251</v>
+      </c>
+      <c r="E45" t="s">
+        <v>454</v>
+      </c>
+      <c r="F45" t="s">
+        <v>455</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>457</v>
+      </c>
+      <c r="B46" t="s">
+        <v>458</v>
+      </c>
+      <c r="C46" t="s">
+        <v>459</v>
+      </c>
+      <c r="D46" t="s">
+        <v>225</v>
+      </c>
+      <c r="E46" t="s">
+        <v>460</v>
+      </c>
+      <c r="F46" t="s">
+        <v>461</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>463</v>
+      </c>
+      <c r="B47" t="s">
+        <v>464</v>
+      </c>
+      <c r="C47" t="s">
+        <v>465</v>
+      </c>
+      <c r="D47" t="s">
+        <v>225</v>
+      </c>
+      <c r="E47" t="s">
+        <v>466</v>
+      </c>
+      <c r="F47" t="s">
+        <v>354</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>468</v>
+      </c>
+      <c r="B48" t="s">
+        <v>469</v>
+      </c>
+      <c r="C48" t="s">
+        <v>244</v>
+      </c>
+      <c r="D48" t="s">
+        <v>225</v>
+      </c>
+      <c r="E48" t="s">
+        <v>470</v>
+      </c>
+      <c r="F48" t="s">
+        <v>471</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>473</v>
+      </c>
+      <c r="B49" t="s">
+        <v>474</v>
+      </c>
+      <c r="C49" t="s">
+        <v>475</v>
+      </c>
+      <c r="D49" t="s">
+        <v>225</v>
+      </c>
+      <c r="E49" t="s">
+        <v>476</v>
+      </c>
+      <c r="F49" t="s">
+        <v>477</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>479</v>
+      </c>
+      <c r="B50" t="s">
+        <v>480</v>
+      </c>
+      <c r="C50" t="s">
+        <v>481</v>
+      </c>
+      <c r="D50" t="s">
+        <v>225</v>
+      </c>
+      <c r="E50" t="s">
+        <v>482</v>
+      </c>
+      <c r="F50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>484</v>
+      </c>
+      <c r="B51" t="s">
+        <v>485</v>
+      </c>
+      <c r="C51" t="s">
+        <v>274</v>
+      </c>
+      <c r="D51" t="s">
+        <v>225</v>
+      </c>
+      <c r="E51" t="s">
+        <v>312</v>
+      </c>
+      <c r="F51" t="s">
+        <v>486</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>488</v>
+      </c>
+      <c r="B52" t="s">
+        <v>489</v>
+      </c>
+      <c r="C52" t="s">
+        <v>490</v>
+      </c>
+      <c r="D52" t="s">
+        <v>225</v>
+      </c>
+      <c r="E52" t="s">
+        <v>491</v>
+      </c>
+      <c r="F52" t="s">
+        <v>492</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>494</v>
+      </c>
+      <c r="B53" t="s">
+        <v>495</v>
+      </c>
+      <c r="C53" t="s">
+        <v>353</v>
+      </c>
+      <c r="D53" t="s">
+        <v>225</v>
+      </c>
+      <c r="E53" t="s">
+        <v>496</v>
+      </c>
+      <c r="F53" t="s">
+        <v>497</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>499</v>
+      </c>
+      <c r="B54" t="s">
+        <v>500</v>
+      </c>
+      <c r="C54" t="s">
+        <v>399</v>
+      </c>
+      <c r="D54" t="s">
+        <v>225</v>
+      </c>
+      <c r="E54" t="s">
+        <v>501</v>
+      </c>
+      <c r="F54" t="s">
+        <v>502</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>504</v>
+      </c>
+      <c r="B55" t="s">
+        <v>357</v>
+      </c>
+      <c r="C55" t="s">
+        <v>505</v>
+      </c>
+      <c r="D55" t="s">
+        <v>225</v>
+      </c>
+      <c r="E55" t="s">
+        <v>506</v>
+      </c>
+      <c r="F55" t="s">
+        <v>507</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>509</v>
+      </c>
+      <c r="B56" t="s">
+        <v>510</v>
+      </c>
+      <c r="C56" t="s">
+        <v>274</v>
+      </c>
+      <c r="D56" t="s">
+        <v>225</v>
+      </c>
+      <c r="E56" t="s">
+        <v>511</v>
+      </c>
+      <c r="F56" t="s">
+        <v>240</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>513</v>
+      </c>
+      <c r="B57" t="s">
+        <v>514</v>
+      </c>
+      <c r="C57" t="s">
+        <v>353</v>
+      </c>
+      <c r="D57" t="s">
+        <v>225</v>
+      </c>
+      <c r="E57" t="s">
+        <v>515</v>
+      </c>
+      <c r="F57" t="s">
+        <v>516</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>518</v>
+      </c>
+      <c r="B58" t="s">
+        <v>519</v>
+      </c>
+      <c r="C58" t="s">
+        <v>274</v>
+      </c>
+      <c r="D58" t="s">
+        <v>225</v>
+      </c>
+      <c r="E58" t="s">
+        <v>520</v>
+      </c>
+      <c r="F58" t="s">
+        <v>521</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>523</v>
+      </c>
+      <c r="B59" t="s">
+        <v>524</v>
+      </c>
+      <c r="C59" t="s">
+        <v>525</v>
+      </c>
+      <c r="D59" t="s">
+        <v>225</v>
+      </c>
+      <c r="E59" t="s">
+        <v>526</v>
+      </c>
+      <c r="F59" t="s">
+        <v>527</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>529</v>
+      </c>
+      <c r="B60" t="s">
+        <v>530</v>
+      </c>
+      <c r="C60" t="s">
+        <v>531</v>
+      </c>
+      <c r="D60" t="s">
+        <v>532</v>
+      </c>
+      <c r="E60" t="s">
+        <v>276</v>
+      </c>
+      <c r="F60" t="s">
+        <v>533</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>535</v>
+      </c>
+      <c r="B61" t="s">
+        <v>536</v>
+      </c>
+      <c r="C61" t="s">
+        <v>537</v>
+      </c>
+      <c r="D61" t="s">
+        <v>251</v>
+      </c>
+      <c r="E61" t="s">
+        <v>538</v>
+      </c>
+      <c r="F61" t="s">
+        <v>539</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>541</v>
+      </c>
+      <c r="B62" t="s">
+        <v>542</v>
+      </c>
+      <c r="C62" t="s">
+        <v>353</v>
+      </c>
+      <c r="D62" t="s">
+        <v>225</v>
+      </c>
+      <c r="E62" t="s">
+        <v>543</v>
+      </c>
+      <c r="F62" t="s">
+        <v>276</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>545</v>
+      </c>
+      <c r="B63" t="s">
+        <v>546</v>
+      </c>
+      <c r="C63" t="s">
+        <v>353</v>
+      </c>
+      <c r="D63" t="s">
+        <v>251</v>
+      </c>
+      <c r="E63" t="s">
+        <v>547</v>
+      </c>
+      <c r="F63" t="s">
+        <v>548</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>550</v>
+      </c>
+      <c r="B64" t="s">
+        <v>551</v>
+      </c>
+      <c r="C64" t="s">
+        <v>384</v>
+      </c>
+      <c r="D64" t="s">
+        <v>251</v>
+      </c>
+      <c r="E64" t="s">
+        <v>552</v>
+      </c>
+      <c r="F64" t="s">
+        <v>553</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>555</v>
+      </c>
+      <c r="B65" t="s">
+        <v>556</v>
+      </c>
+      <c r="C65" t="s">
+        <v>353</v>
+      </c>
+      <c r="D65" t="s">
+        <v>225</v>
+      </c>
+      <c r="E65" t="s">
+        <v>276</v>
+      </c>
+      <c r="F65" t="s">
+        <v>557</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>559</v>
+      </c>
+      <c r="B66" t="s">
+        <v>560</v>
+      </c>
+      <c r="C66" t="s">
+        <v>274</v>
+      </c>
+      <c r="D66" t="s">
+        <v>225</v>
+      </c>
+      <c r="E66" t="s">
+        <v>561</v>
+      </c>
+      <c r="F66" t="s">
+        <v>562</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>564</v>
+      </c>
+      <c r="B67" t="s">
+        <v>565</v>
+      </c>
+      <c r="C67" t="s">
+        <v>490</v>
+      </c>
+      <c r="D67" t="s">
+        <v>225</v>
+      </c>
+      <c r="E67" t="s">
+        <v>566</v>
+      </c>
+      <c r="F67" t="s">
+        <v>567</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>569</v>
+      </c>
+      <c r="B68" t="s">
+        <v>570</v>
+      </c>
+      <c r="C68" t="s">
+        <v>358</v>
+      </c>
+      <c r="D68" t="s">
+        <v>251</v>
+      </c>
+      <c r="E68" t="s">
+        <v>286</v>
+      </c>
+      <c r="F68" t="s">
+        <v>571</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>573</v>
+      </c>
+      <c r="B69" t="s">
+        <v>574</v>
+      </c>
+      <c r="C69" t="s">
+        <v>333</v>
+      </c>
+      <c r="D69" t="s">
+        <v>251</v>
+      </c>
+      <c r="E69" t="s">
+        <v>575</v>
+      </c>
+      <c r="F69" t="s">
+        <v>455</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>577</v>
+      </c>
+      <c r="B70" t="s">
+        <v>578</v>
+      </c>
+      <c r="C70" t="s">
+        <v>244</v>
+      </c>
+      <c r="D70" t="s">
+        <v>251</v>
+      </c>
+      <c r="E70" t="s">
+        <v>579</v>
+      </c>
+      <c r="F70" t="s">
+        <v>276</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>581</v>
+      </c>
+      <c r="B71" t="s">
+        <v>582</v>
+      </c>
+      <c r="C71" t="s">
+        <v>274</v>
+      </c>
+      <c r="D71" t="s">
+        <v>251</v>
+      </c>
+      <c r="E71" t="s">
+        <v>583</v>
+      </c>
+      <c r="F71" t="s">
+        <v>497</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>585</v>
+      </c>
+      <c r="B72" t="s">
+        <v>578</v>
+      </c>
+      <c r="C72" t="s">
+        <v>244</v>
+      </c>
+      <c r="D72" t="s">
+        <v>251</v>
+      </c>
+      <c r="E72" t="s">
+        <v>586</v>
+      </c>
+      <c r="F72" t="s">
+        <v>587</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>589</v>
+      </c>
+      <c r="B73" t="s">
+        <v>489</v>
+      </c>
+      <c r="C73" t="s">
+        <v>490</v>
+      </c>
+      <c r="D73" t="s">
+        <v>225</v>
+      </c>
+      <c r="E73" t="s">
+        <v>590</v>
+      </c>
+      <c r="F73" t="s">
+        <v>492</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>592</v>
+      </c>
+      <c r="B74" t="s">
+        <v>593</v>
+      </c>
+      <c r="C74" t="s">
+        <v>40</v>
+      </c>
+      <c r="D74" t="s">
+        <v>225</v>
+      </c>
+      <c r="E74" t="s">
+        <v>594</v>
+      </c>
+      <c r="F74" t="s">
+        <v>595</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>597</v>
+      </c>
+      <c r="B75" t="s">
+        <v>598</v>
+      </c>
+      <c r="C75" t="s">
+        <v>353</v>
+      </c>
+      <c r="D75" t="s">
+        <v>225</v>
+      </c>
+      <c r="E75" t="s">
+        <v>599</v>
+      </c>
+      <c r="F75" t="s">
+        <v>276</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>601</v>
+      </c>
+      <c r="B76" t="s">
+        <v>602</v>
+      </c>
+      <c r="C76" t="s">
+        <v>603</v>
+      </c>
+      <c r="D76" t="s">
+        <v>225</v>
+      </c>
+      <c r="E76" t="s">
+        <v>454</v>
+      </c>
+      <c r="F76" t="s">
+        <v>604</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>606</v>
+      </c>
+      <c r="B77" t="s">
+        <v>607</v>
+      </c>
+      <c r="C77" t="s">
+        <v>274</v>
+      </c>
+      <c r="D77" t="s">
+        <v>225</v>
+      </c>
+      <c r="E77" t="s">
+        <v>608</v>
+      </c>
+      <c r="F77" t="s">
+        <v>609</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>611</v>
+      </c>
+      <c r="B78" t="s">
+        <v>612</v>
+      </c>
+      <c r="C78" t="s">
+        <v>613</v>
+      </c>
+      <c r="D78" t="s">
+        <v>225</v>
+      </c>
+      <c r="E78" t="s">
+        <v>614</v>
+      </c>
+      <c r="F78" t="s">
+        <v>615</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>617</v>
+      </c>
+      <c r="B79" t="s">
+        <v>618</v>
+      </c>
+      <c r="C79" t="s">
+        <v>619</v>
+      </c>
+      <c r="D79" t="s">
+        <v>532</v>
+      </c>
+      <c r="E79" t="s">
+        <v>620</v>
+      </c>
+      <c r="F79" t="s">
+        <v>253</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>622</v>
+      </c>
+      <c r="B80" t="s">
+        <v>623</v>
+      </c>
+      <c r="C80" t="s">
+        <v>624</v>
+      </c>
+      <c r="D80" t="s">
+        <v>225</v>
+      </c>
+      <c r="E80" t="s">
+        <v>625</v>
+      </c>
+      <c r="F80" t="s">
+        <v>276</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>627</v>
+      </c>
+      <c r="B81" t="s">
+        <v>556</v>
+      </c>
+      <c r="C81" t="s">
+        <v>353</v>
+      </c>
+      <c r="D81" t="s">
+        <v>225</v>
+      </c>
+      <c r="E81" t="s">
+        <v>276</v>
+      </c>
+      <c r="F81" t="s">
+        <v>557</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>629</v>
+      </c>
+      <c r="B82" t="s">
+        <v>623</v>
+      </c>
+      <c r="C82" t="s">
+        <v>624</v>
+      </c>
+      <c r="D82" t="s">
+        <v>225</v>
+      </c>
+      <c r="E82" t="s">
+        <v>630</v>
+      </c>
+      <c r="F82" t="s">
+        <v>631</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>633</v>
+      </c>
+      <c r="B83" t="s">
+        <v>480</v>
+      </c>
+      <c r="C83" t="s">
+        <v>481</v>
+      </c>
+      <c r="D83" t="s">
+        <v>225</v>
+      </c>
+      <c r="E83" t="s">
+        <v>634</v>
+      </c>
+      <c r="F83" t="s">
+        <v>276</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>636</v>
+      </c>
+      <c r="B84" t="s">
+        <v>276</v>
+      </c>
+      <c r="C84" t="s">
+        <v>637</v>
+      </c>
+      <c r="D84" t="s">
+        <v>225</v>
+      </c>
+      <c r="E84" t="s">
+        <v>638</v>
+      </c>
+      <c r="F84" t="s">
+        <v>639</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>641</v>
+      </c>
+      <c r="B85" t="s">
+        <v>642</v>
+      </c>
+      <c r="C85" t="s">
+        <v>353</v>
+      </c>
+      <c r="D85" t="s">
+        <v>225</v>
+      </c>
+      <c r="E85" t="s">
+        <v>643</v>
+      </c>
+      <c r="F85" t="s">
+        <v>276</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>645</v>
+      </c>
+      <c r="B86" t="s">
+        <v>646</v>
+      </c>
+      <c r="C86" t="s">
+        <v>647</v>
+      </c>
+      <c r="D86" t="s">
+        <v>225</v>
+      </c>
+      <c r="E86" t="s">
+        <v>648</v>
+      </c>
+      <c r="F86" t="s">
+        <v>649</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>651</v>
+      </c>
+      <c r="B87" t="s">
+        <v>652</v>
+      </c>
+      <c r="C87" t="s">
+        <v>481</v>
+      </c>
+      <c r="D87" t="s">
+        <v>225</v>
+      </c>
+      <c r="E87" t="s">
+        <v>653</v>
+      </c>
+      <c r="F87" t="s">
+        <v>276</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>655</v>
+      </c>
+      <c r="B88" t="s">
+        <v>656</v>
+      </c>
+      <c r="C88" t="s">
+        <v>353</v>
+      </c>
+      <c r="D88" t="s">
+        <v>365</v>
+      </c>
+      <c r="E88" t="s">
+        <v>657</v>
+      </c>
+      <c r="F88" t="s">
+        <v>658</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>660</v>
+      </c>
+      <c r="B89" t="s">
+        <v>661</v>
+      </c>
+      <c r="C89" t="s">
+        <v>353</v>
+      </c>
+      <c r="D89" t="s">
+        <v>225</v>
+      </c>
+      <c r="E89" t="s">
+        <v>662</v>
+      </c>
+      <c r="F89" t="s">
+        <v>663</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>665</v>
+      </c>
+      <c r="B90" t="s">
+        <v>519</v>
+      </c>
+      <c r="C90" t="s">
+        <v>274</v>
+      </c>
+      <c r="D90" t="s">
+        <v>225</v>
+      </c>
+      <c r="E90" t="s">
+        <v>666</v>
+      </c>
+      <c r="F90" t="s">
+        <v>667</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>669</v>
+      </c>
+      <c r="B91" t="s">
+        <v>670</v>
+      </c>
+      <c r="C91" t="s">
+        <v>671</v>
+      </c>
+      <c r="D91" t="s">
+        <v>251</v>
+      </c>
+      <c r="E91" t="s">
+        <v>672</v>
+      </c>
+      <c r="F91" t="s">
+        <v>276</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>674</v>
+      </c>
+      <c r="B92" t="s">
+        <v>675</v>
+      </c>
+      <c r="C92" t="s">
+        <v>676</v>
+      </c>
+      <c r="D92" t="s">
+        <v>225</v>
+      </c>
+      <c r="E92" t="s">
+        <v>677</v>
+      </c>
+      <c r="F92" t="s">
+        <v>678</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>680</v>
+      </c>
+      <c r="B93" t="s">
+        <v>681</v>
+      </c>
+      <c r="C93" t="s">
+        <v>307</v>
+      </c>
+      <c r="D93" t="s">
+        <v>251</v>
+      </c>
+      <c r="E93" t="s">
+        <v>682</v>
+      </c>
+      <c r="F93" t="s">
+        <v>486</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>684</v>
+      </c>
+      <c r="B94" t="s">
+        <v>685</v>
+      </c>
+      <c r="C94" t="s">
+        <v>353</v>
+      </c>
+      <c r="D94" t="s">
+        <v>225</v>
+      </c>
+      <c r="E94" t="s">
+        <v>686</v>
+      </c>
+      <c r="F94" t="s">
+        <v>687</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>689</v>
+      </c>
+      <c r="B95" t="s">
+        <v>690</v>
+      </c>
+      <c r="C95" t="s">
+        <v>353</v>
+      </c>
+      <c r="D95" t="s">
+        <v>225</v>
+      </c>
+      <c r="E95" t="s">
+        <v>691</v>
+      </c>
+      <c r="F95" t="s">
+        <v>692</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>694</v>
+      </c>
+      <c r="B96" t="s">
+        <v>519</v>
+      </c>
+      <c r="C96" t="s">
+        <v>274</v>
+      </c>
+      <c r="D96" t="s">
+        <v>225</v>
+      </c>
+      <c r="E96" t="s">
+        <v>695</v>
+      </c>
+      <c r="F96" t="s">
+        <v>696</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>698</v>
+      </c>
+      <c r="B97" t="s">
+        <v>338</v>
+      </c>
+      <c r="C97" t="s">
+        <v>339</v>
+      </c>
+      <c r="D97" t="s">
+        <v>225</v>
+      </c>
+      <c r="E97" t="s">
+        <v>699</v>
+      </c>
+      <c r="F97" t="s">
+        <v>227</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>701</v>
+      </c>
+      <c r="B98" t="s">
+        <v>338</v>
+      </c>
+      <c r="C98" t="s">
+        <v>339</v>
+      </c>
+      <c r="D98" t="s">
+        <v>225</v>
+      </c>
+      <c r="E98" t="s">
+        <v>702</v>
+      </c>
+      <c r="F98" t="s">
+        <v>227</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>704</v>
+      </c>
+      <c r="B99" t="s">
+        <v>480</v>
+      </c>
+      <c r="C99" t="s">
+        <v>481</v>
+      </c>
+      <c r="D99" t="s">
+        <v>225</v>
+      </c>
+      <c r="E99" t="s">
+        <v>608</v>
+      </c>
+      <c r="F99" t="s">
+        <v>276</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>706</v>
+      </c>
+      <c r="B100" t="s">
+        <v>338</v>
+      </c>
+      <c r="C100" t="s">
+        <v>339</v>
+      </c>
+      <c r="D100" t="s">
+        <v>225</v>
+      </c>
+      <c r="E100" t="s">
+        <v>707</v>
+      </c>
+      <c r="F100" t="s">
+        <v>227</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>709</v>
+      </c>
+      <c r="B101" t="s">
+        <v>710</v>
+      </c>
+      <c r="C101" t="s">
+        <v>353</v>
+      </c>
+      <c r="D101" t="s">
+        <v>225</v>
+      </c>
+      <c r="E101" t="s">
+        <v>711</v>
+      </c>
+      <c r="F101" t="s">
+        <v>276</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>713</v>
+      </c>
+      <c r="B102" t="s">
+        <v>714</v>
+      </c>
+      <c r="C102" t="s">
+        <v>715</v>
+      </c>
+      <c r="D102" t="s">
+        <v>365</v>
+      </c>
+      <c r="E102" t="s">
+        <v>716</v>
+      </c>
+      <c r="F102" t="s">
+        <v>717</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>719</v>
+      </c>
+      <c r="B103" t="s">
+        <v>410</v>
+      </c>
+      <c r="C103" t="s">
+        <v>274</v>
+      </c>
+      <c r="D103" t="s">
+        <v>225</v>
+      </c>
+      <c r="E103" t="s">
+        <v>720</v>
+      </c>
+      <c r="F103" t="s">
+        <v>276</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>722</v>
+      </c>
+      <c r="B104" t="s">
+        <v>723</v>
+      </c>
+      <c r="C104" t="s">
+        <v>244</v>
+      </c>
+      <c r="D104" t="s">
+        <v>225</v>
+      </c>
+      <c r="E104" t="s">
+        <v>724</v>
+      </c>
+      <c r="F104" t="s">
+        <v>507</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>726</v>
+      </c>
+      <c r="B105" t="s">
+        <v>727</v>
+      </c>
+      <c r="C105" t="s">
+        <v>364</v>
+      </c>
+      <c r="D105" t="s">
+        <v>225</v>
+      </c>
+      <c r="E105" t="s">
+        <v>728</v>
+      </c>
+      <c r="F105" t="s">
+        <v>276</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>729</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-05.xlsx
+++ b/docs/xlsx/jobs-2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="807">
   <si>
     <t>Title</t>
   </si>
@@ -742,6 +742,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/239f0604e0014b3782f9ba2fbbdff85a-administrative-secretary-south-coastal-counties-legal-services-inc-new-bedford</t>
   </si>
   <si>
+    <t>Advancement Associate</t>
+  </si>
+  <si>
+    <t>Mount Tamalpais College</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fa028f99f6b4d9e87ed649f591279c4-advancement-associate-mount-tamalpais-college-san-rafael</t>
+  </si>
+  <si>
     <t>Advocacy &amp; Communications Manager</t>
   </si>
   <si>
@@ -781,6 +799,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ae5c932489e5487abfdc8cc9a4db554b-advocacy-coordinator-bike-east-bay-oakland</t>
   </si>
   <si>
+    <t>Ambassador Program Impact Manager</t>
+  </si>
+  <si>
+    <t>Represent Justice</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d084a10537a545478d1e365c33e0169f-ambassador-program-impact-manager-represent-justice-los-angeles</t>
+  </si>
+  <si>
     <t>Assistant Director - Animalearn</t>
   </si>
   <si>
@@ -799,6 +835,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/bcf0204ca86e4be0b267e2c07c1a7df7-assistant-director-animalearn-american-anti-vivisection-society-jenkintown</t>
   </si>
   <si>
+    <t>Associate Producer</t>
+  </si>
+  <si>
+    <t>Brave New Films</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6719db56b394ac8945a42436225dc85-associate-producer-brave-new-films-los-angeles</t>
+  </si>
+  <si>
     <t>ASSOCIATE SUPERVISING ATTORNEY, REMOVAL DEFENSE PROJECT</t>
   </si>
   <si>
@@ -832,6 +883,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/ee34938e8d1b4e8db9a38f7b7c38c514-associate-fundraising-human-rights-watch-stockholm</t>
   </si>
   <si>
+    <t>Attorney - Lawyers Preventing and Ending Homelessness Project (PEHP)</t>
+  </si>
+  <si>
+    <t>Neighborhood Legal Services of Los Angeles County</t>
+  </si>
+  <si>
+    <t>El Monte, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f67750a919ae45a78d4ea260b8eb3739-attorney-lawyers-preventing-and-ending-homelessness-project-pehp-neighborhood-legal-services-of-los-angeles-county-el-monte</t>
+  </si>
+  <si>
+    <t>Attorney – Stay Housed LA Program</t>
+  </si>
+  <si>
+    <t>Glendale, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db456e099c574a488560cfebb76464b6-attorney-stay-housed-la-program-neighborhood-legal-services-of-los-angeles-county-glendale</t>
+  </si>
+  <si>
+    <t>Attorney Network Coordinator</t>
+  </si>
+  <si>
+    <t>Partnership for Civil Justice</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1707dd33623b46db9fb28de2f8152e98-attorney-network-coordinator-partnership-for-civil-justice-washington</t>
+  </si>
+  <si>
+    <t>Attorney- Family Law</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/779d3e837a0f44c5afca90c61d1d9ece-attorney-family-law-neighborhood-legal-services-of-los-angeles-county-los-angeles</t>
+  </si>
+  <si>
+    <t>Attorney- Shriver Housing Project Los Angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b3d67c22caa047b7941f58210096cb8e-attorney-shriver-housing-project-los-angeles-neighborhood-legal-services-of-los-angeles-county-los-angeles</t>
+  </si>
+  <si>
+    <t>Attorney- Van Nuys- Eviction Diversion Pilot Project</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92582b83d6664d8fa93cb5fd04ebccf5-attorney-van-nuys-eviction-diversion-pilot-project-neighborhood-legal-services-of-los-angeles-county-los-angeles</t>
+  </si>
+  <si>
     <t>Bilingual Housing Case Manager</t>
   </si>
   <si>
@@ -931,6 +1048,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/4a9cc75cd1be4232837e3a7021b9b9a5-chief-finance-and-administration-officer-new-york-common-pantry-new-york</t>
   </si>
   <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Envision Consulting</t>
+  </si>
+  <si>
+    <t>USD 205000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/e279ccf722204a17a3da3b5a6dccb9e3-chief-financial-officer-envision-consulting-los-angeles</t>
+  </si>
+  <si>
     <t>Chief Operating Officer</t>
   </si>
   <si>
@@ -1075,9 +1207,6 @@
     <t>Huntington's Disease Youth Organization</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Children Youth, Education, Family</t>
   </si>
   <si>
@@ -1123,6 +1252,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b0be82d28b2644af88b47a4f89ae71db-corporate-partnerships-associate-chicago-il-rescuing-leftover-cuisine-chicago</t>
   </si>
   <si>
+    <t>Data Centers Community Organizer</t>
+  </si>
+  <si>
+    <t>Columbia Riverkeeper</t>
+  </si>
+  <si>
+    <t>Hood River, Oregon</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de47cc703e5d485995298a53ddb216a5-data-centers-community-organizer-columbia-riverkeeper-hood-river</t>
+  </si>
+  <si>
     <t>Data Engineer, Data and Insights</t>
   </si>
   <si>
@@ -1207,6 +1354,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/2e2eb94cf5184dcfaa78d7f0611d0f3d-digital-skilling-program-coordinator-hispanic-federation-new-york</t>
   </si>
   <si>
+    <t>Director of Housing &amp; Homelessness Prevention</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 148000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75fa5f363ce2424cb0f8357dce2beba5-director-of-housing-homelessness-prevention-neighborhood-legal-services-of-los-angeles-county-glendale</t>
+  </si>
+  <si>
     <t>Director of Housing Stability Services</t>
   </si>
   <si>
@@ -1225,6 +1381,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/dd006b4af3634852a52116f7b0871f65-director-of-housing-stability-services-arm-in-arm-hamilton-township</t>
   </si>
   <si>
+    <t>Director of Human Resources</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 163000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d11ab9a6d5134ebab0f1a77259158e49-director-of-human-resources-neighborhood-legal-services-of-los-angeles-county-glendale</t>
+  </si>
+  <si>
     <t>Director of Marketing and Community Engagement</t>
   </si>
   <si>
@@ -1243,6 +1408,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/e1fce64627324b36a8f37037bed94756-director-of-marketing-and-community-engagement-spca-westchester-briarcliff-manor</t>
   </si>
   <si>
+    <t>DIRECTOR OF SUMMER RESIDENTIAL PROGRAMS &amp; ENRICHMENT</t>
+  </si>
+  <si>
+    <t>The AnBryce Foundation</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8266c3df764462cb58030944e5de05b-director-of-summer-residential-programs-enrichment-the-anbryce-foundation-washington</t>
+  </si>
+  <si>
     <t>Director, Human Resources Operations</t>
   </si>
   <si>
@@ -1273,6 +1453,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/7ba13a03982c4066aeb29379a0a26aab-domestic-violence-response-team-coordinator-women-aware-inc-new-brunswick</t>
   </si>
   <si>
+    <t>Educational Facilitator</t>
+  </si>
+  <si>
+    <t>K9 Youth Alliance</t>
+  </si>
+  <si>
+    <t>USD 20.50 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c57969226c348d395973cec9c8f164a-educational-facilitator-k9-youth-alliance-los-angeles</t>
+  </si>
+  <si>
     <t>Engineering Expo and Events Coordinator</t>
   </si>
   <si>
@@ -1336,6 +1531,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/70da3a974f60471289ff453a661713ad-executive-director-tupelo-press-north-adams</t>
   </si>
   <si>
+    <t>Executive Director - CHNSC</t>
+  </si>
+  <si>
+    <t>Center for Empowered Politics Education Fund</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9175864ec4f0444399b42747194a8404-executive-director-chnsc-center-for-empowered-politics-education-fund-oakland</t>
+  </si>
+  <si>
     <t>Executive Director at National Network of Abortion Funds</t>
   </si>
   <si>
@@ -1426,9 +1633,6 @@
     <t>CAMBA</t>
   </si>
   <si>
-    <t>USD 80000.00 - 90000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Community Development, Economic Development</t>
   </si>
   <si>
@@ -1603,6 +1807,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/0502d25afa8645009d1b4998e44929f5-managing-director-central-florida-blessings-in-a-backpack-orlando</t>
   </si>
   <si>
+    <t>Managing Family Law Attorney</t>
+  </si>
+  <si>
+    <t>Open Door Legal</t>
+  </si>
+  <si>
+    <t>USD 89500.00 - 111500.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/609db795bc9d4aa897d01d454023f385-managing-family-law-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
     <t>Maryland Coastal Fellowships</t>
   </si>
   <si>
@@ -1612,9 +1831,6 @@
     <t>Annapolis, Maryland</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>Environment</t>
   </si>
   <si>
@@ -1876,9 +2092,6 @@
     <t>Allentown, Pennsylvania</t>
   </si>
   <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5f91aa1d2448419c8db489c0a09f346f-project-manager-the-allentown-parknership-allentown</t>
   </si>
   <si>
@@ -2044,9 +2257,6 @@
     <t>Better Angels</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 57000.00 - 63000.00/year</t>
   </si>
   <si>
@@ -2134,6 +2344,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/ca00dab425794640b6006338338d84fd-street-outreach-manager-bethesda-cares-inc-bethesda</t>
   </si>
   <si>
+    <t>Supervising Attorney – Van Nuys - Eviction Diversion Pilot Project</t>
+  </si>
+  <si>
+    <t>USD 109000.00 - 127000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/748d1766c6a84279ba90ee4d32b30b49-supervising-attorney-van-nuys-eviction-diversion-pilot-project-neighborhood-legal-services-of-los-angeles-county-los-angeles</t>
+  </si>
+  <si>
     <t>Supervising Staff Attorney, Preserving Affordable Housing - Brooklyn</t>
   </si>
   <si>
@@ -2155,6 +2374,21 @@
     <t>https://www.idealist.org/en/business-job/8650e7ff06dc4963a92ac1d6d319d371-systems-change-policy-strategy-manager-rebel-heart-therapy-portland</t>
   </si>
   <si>
+    <t>Technology Coordinator, NASS Program</t>
+  </si>
+  <si>
+    <t>National Association of State Departments of Agriculture</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50330188b43e473e87fb2503b5864fd4-technology-coordinator-nass-program-national-association-of-state-departments-of-agriculture-arlington</t>
+  </si>
+  <si>
     <t>Temporary Housing Attorney</t>
   </si>
   <si>
@@ -2165,9 +2399,6 @@
   </si>
   <si>
     <t>USD 1655.00 - 2177.00/week</t>
-  </si>
-  <si>
-    <t>Housing Homelessness, Legal Assistance, Poverty</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/4283e1aacb9b48a68c81ba565c6c8051-temporary-housing-attorney-legal-aid-society-of-san-mateo-county-redwood-city</t>
@@ -3743,7 +3974,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3885,30 +4116,30 @@
         <v>250</v>
       </c>
       <c r="D6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" t="s">
         <v>251</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>252</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" t="s">
         <v>255</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>256</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>257</v>
-      </c>
-      <c r="D7" t="s">
-        <v>225</v>
       </c>
       <c r="E7" t="s">
         <v>258</v>
@@ -3928,53 +4159,53 @@
         <v>262</v>
       </c>
       <c r="C8" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="D8" t="s">
         <v>225</v>
       </c>
       <c r="E8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D9" t="s">
         <v>225</v>
       </c>
       <c r="E9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C10" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="D10" t="s">
         <v>225</v>
@@ -3997,16 +4228,16 @@
         <v>279</v>
       </c>
       <c r="C11" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E11" t="s">
         <v>280</v>
       </c>
-      <c r="D11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>281</v>
-      </c>
-      <c r="F11" t="s">
-        <v>276</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>282</v>
@@ -4063,1606 +4294,1606 @@
         <v>295</v>
       </c>
       <c r="B14" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" t="s">
         <v>296</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" t="s">
+        <v>292</v>
+      </c>
+      <c r="F14" t="s">
+        <v>293</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="D14" t="s">
-        <v>225</v>
-      </c>
-      <c r="E14" t="s">
-        <v>298</v>
-      </c>
-      <c r="F14" t="s">
-        <v>299</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>298</v>
+      </c>
+      <c r="B15" t="s">
+        <v>299</v>
+      </c>
+      <c r="C15" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F15" t="s">
+        <v>300</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="B15" t="s">
-        <v>302</v>
-      </c>
-      <c r="C15" t="s">
-        <v>274</v>
-      </c>
-      <c r="D15" t="s">
-        <v>225</v>
-      </c>
-      <c r="E15" t="s">
-        <v>303</v>
-      </c>
-      <c r="F15" t="s">
-        <v>276</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C16" t="s">
+        <v>303</v>
+      </c>
+      <c r="D16" t="s">
+        <v>225</v>
+      </c>
+      <c r="E16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F16" t="s">
+        <v>304</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="B16" t="s">
-        <v>306</v>
-      </c>
-      <c r="C16" t="s">
-        <v>307</v>
-      </c>
-      <c r="D16" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" t="s">
-        <v>308</v>
-      </c>
-      <c r="F16" t="s">
-        <v>276</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="C17" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D17" t="s">
         <v>225</v>
       </c>
       <c r="E17" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="F17" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B18" t="s">
-        <v>223</v>
+        <v>290</v>
       </c>
       <c r="C18" t="s">
-        <v>224</v>
+        <v>303</v>
       </c>
       <c r="D18" t="s">
-        <v>225</v>
+        <v>309</v>
       </c>
       <c r="E18" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="F18" t="s">
-        <v>227</v>
+        <v>293</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B19" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C19" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="D19" t="s">
         <v>225</v>
       </c>
       <c r="E19" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F19" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>317</v>
+      </c>
+      <c r="B20" t="s">
+        <v>318</v>
+      </c>
+      <c r="C20" t="s">
+        <v>319</v>
+      </c>
+      <c r="D20" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" t="s">
+        <v>320</v>
+      </c>
+      <c r="F20" t="s">
+        <v>315</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="B20" t="s">
-        <v>322</v>
-      </c>
-      <c r="C20" t="s">
-        <v>323</v>
-      </c>
-      <c r="D20" t="s">
-        <v>225</v>
-      </c>
-      <c r="E20" t="s">
-        <v>324</v>
-      </c>
-      <c r="F20" t="s">
-        <v>276</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>322</v>
+      </c>
+      <c r="B21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C21" t="s">
+        <v>324</v>
+      </c>
+      <c r="D21" t="s">
+        <v>225</v>
+      </c>
+      <c r="E21" t="s">
+        <v>325</v>
+      </c>
+      <c r="F21" t="s">
         <v>326</v>
       </c>
-      <c r="B21" t="s">
+      <c r="H21" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C21" t="s">
-        <v>274</v>
-      </c>
-      <c r="D21" t="s">
-        <v>225</v>
-      </c>
-      <c r="E21" t="s">
-        <v>328</v>
-      </c>
-      <c r="F21" t="s">
-        <v>329</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>328</v>
+      </c>
+      <c r="B22" t="s">
+        <v>329</v>
+      </c>
+      <c r="C22" t="s">
+        <v>330</v>
+      </c>
+      <c r="D22" t="s">
+        <v>225</v>
+      </c>
+      <c r="E22" t="s">
         <v>331</v>
       </c>
-      <c r="B22" t="s">
+      <c r="F22" t="s">
         <v>332</v>
       </c>
-      <c r="C22" t="s">
+      <c r="H22" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="D22" t="s">
-        <v>225</v>
-      </c>
-      <c r="E22" t="s">
-        <v>334</v>
-      </c>
-      <c r="F22" t="s">
-        <v>335</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>334</v>
+      </c>
+      <c r="B23" t="s">
+        <v>335</v>
+      </c>
+      <c r="C23" t="s">
+        <v>336</v>
+      </c>
+      <c r="D23" t="s">
+        <v>225</v>
+      </c>
+      <c r="E23" t="s">
         <v>337</v>
       </c>
-      <c r="B23" t="s">
+      <c r="F23" t="s">
         <v>338</v>
       </c>
-      <c r="C23" t="s">
+      <c r="H23" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="D23" t="s">
-        <v>225</v>
-      </c>
-      <c r="E23" t="s">
-        <v>340</v>
-      </c>
-      <c r="F23" t="s">
-        <v>227</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>340</v>
+      </c>
+      <c r="B24" t="s">
+        <v>341</v>
+      </c>
+      <c r="C24" t="s">
+        <v>313</v>
+      </c>
+      <c r="D24" t="s">
+        <v>225</v>
+      </c>
+      <c r="E24" t="s">
         <v>342</v>
       </c>
-      <c r="B24" t="s">
+      <c r="F24" t="s">
+        <v>315</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="C24" t="s">
-        <v>344</v>
-      </c>
-      <c r="D24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E24" t="s">
-        <v>276</v>
-      </c>
-      <c r="F24" t="s">
-        <v>345</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>344</v>
+      </c>
+      <c r="B25" t="s">
+        <v>345</v>
+      </c>
+      <c r="C25" t="s">
+        <v>303</v>
+      </c>
+      <c r="D25" t="s">
+        <v>225</v>
+      </c>
+      <c r="E25" t="s">
+        <v>346</v>
+      </c>
+      <c r="F25" t="s">
         <v>347</v>
       </c>
-      <c r="B25" t="s">
-        <v>273</v>
-      </c>
-      <c r="C25" t="s">
-        <v>274</v>
-      </c>
-      <c r="D25" t="s">
-        <v>251</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="H25" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="F25" t="s">
-        <v>349</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>349</v>
+      </c>
+      <c r="B26" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" t="s">
         <v>351</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
+        <v>225</v>
+      </c>
+      <c r="E26" t="s">
         <v>352</v>
       </c>
-      <c r="C26" t="s">
+      <c r="F26" t="s">
+        <v>315</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="D26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E26" t="s">
-        <v>276</v>
-      </c>
-      <c r="F26" t="s">
-        <v>354</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>349</v>
+      </c>
+      <c r="B27" t="s">
+        <v>354</v>
+      </c>
+      <c r="C27" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" t="s">
+        <v>225</v>
+      </c>
+      <c r="E27" t="s">
         <v>356</v>
       </c>
-      <c r="B27" t="s">
+      <c r="F27" t="s">
         <v>357</v>
       </c>
-      <c r="C27" t="s">
+      <c r="H27" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="D27" t="s">
-        <v>251</v>
-      </c>
-      <c r="E27" t="s">
-        <v>359</v>
-      </c>
-      <c r="F27" t="s">
-        <v>360</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B28" t="s">
-        <v>363</v>
+        <v>223</v>
       </c>
       <c r="C28" t="s">
-        <v>364</v>
+        <v>224</v>
       </c>
       <c r="D28" t="s">
-        <v>365</v>
+        <v>225</v>
       </c>
       <c r="E28" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="F28" t="s">
-        <v>367</v>
+        <v>227</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B29" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="C29" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="D29" t="s">
         <v>225</v>
       </c>
       <c r="E29" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="F29" t="s">
-        <v>372</v>
+        <v>315</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B30" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C30" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="D30" t="s">
         <v>225</v>
       </c>
       <c r="E30" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="F30" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B31" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="C31" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="D31" t="s">
         <v>225</v>
       </c>
       <c r="E31" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F31" t="s">
-        <v>227</v>
+        <v>373</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C32" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D32" t="s">
         <v>225</v>
       </c>
       <c r="E32" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="F32" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B33" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C33" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="D33" t="s">
         <v>225</v>
       </c>
       <c r="E33" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="F33" t="s">
-        <v>391</v>
+        <v>227</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B34" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C34" t="s">
-        <v>274</v>
+        <v>388</v>
       </c>
       <c r="D34" t="s">
         <v>225</v>
       </c>
       <c r="E34" t="s">
-        <v>395</v>
+        <v>315</v>
       </c>
       <c r="F34" t="s">
-        <v>276</v>
+        <v>389</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B35" t="s">
-        <v>398</v>
+        <v>312</v>
       </c>
       <c r="C35" t="s">
-        <v>399</v>
+        <v>313</v>
       </c>
       <c r="D35" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E35" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="F35" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B36" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C36" t="s">
-        <v>405</v>
+        <v>263</v>
       </c>
       <c r="D36" t="s">
         <v>225</v>
       </c>
       <c r="E36" t="s">
-        <v>406</v>
+        <v>315</v>
       </c>
       <c r="F36" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="B37" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C37" t="s">
-        <v>274</v>
+        <v>401</v>
       </c>
       <c r="D37" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E37" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="F37" t="s">
-        <v>276</v>
+        <v>403</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B38" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C38" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="D38" t="s">
-        <v>225</v>
+        <v>408</v>
       </c>
       <c r="E38" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="F38" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B39" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C39" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="D39" t="s">
         <v>225</v>
       </c>
       <c r="E39" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="F39" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B40" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C40" t="s">
-        <v>426</v>
+        <v>313</v>
       </c>
       <c r="D40" t="s">
         <v>225</v>
       </c>
       <c r="E40" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F40" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B41" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C41" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="D41" t="s">
         <v>225</v>
       </c>
       <c r="E41" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F41" t="s">
-        <v>434</v>
+        <v>315</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>428</v>
       </c>
       <c r="B42" t="s">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="C42" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="D42" t="s">
         <v>225</v>
       </c>
       <c r="E42" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="F42" t="s">
-        <v>438</v>
+        <v>227</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="B43" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C43" t="s">
-        <v>353</v>
+        <v>433</v>
       </c>
       <c r="D43" t="s">
         <v>225</v>
       </c>
       <c r="E43" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="F43" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B44" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C44" t="s">
-        <v>447</v>
+        <v>263</v>
       </c>
       <c r="D44" t="s">
         <v>225</v>
       </c>
       <c r="E44" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="F44" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B45" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="C45" t="s">
-        <v>453</v>
+        <v>313</v>
       </c>
       <c r="D45" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E45" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F45" t="s">
-        <v>455</v>
+        <v>315</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="B46" t="s">
-        <v>458</v>
+        <v>290</v>
       </c>
       <c r="C46" t="s">
-        <v>459</v>
+        <v>296</v>
       </c>
       <c r="D46" t="s">
         <v>225</v>
       </c>
       <c r="E46" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="F46" t="s">
-        <v>461</v>
+        <v>293</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="B47" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="C47" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="D47" t="s">
         <v>225</v>
       </c>
       <c r="E47" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="F47" t="s">
-        <v>354</v>
+        <v>453</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s">
-        <v>469</v>
+        <v>290</v>
       </c>
       <c r="C48" t="s">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="D48" t="s">
         <v>225</v>
       </c>
       <c r="E48" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="F48" t="s">
-        <v>471</v>
+        <v>240</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="B49" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="C49" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="D49" t="s">
         <v>225</v>
       </c>
       <c r="E49" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="F49" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B50" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="C50" t="s">
-        <v>481</v>
+        <v>351</v>
       </c>
       <c r="D50" t="s">
         <v>225</v>
       </c>
       <c r="E50" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="F50" t="s">
-        <v>276</v>
+        <v>467</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="B51" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="C51" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="D51" t="s">
         <v>225</v>
       </c>
       <c r="E51" t="s">
-        <v>312</v>
+        <v>471</v>
       </c>
       <c r="F51" t="s">
-        <v>486</v>
+        <v>315</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="B52" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="C52" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="D52" t="s">
         <v>225</v>
       </c>
       <c r="E52" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="F52" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="C53" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D53" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E53" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="F53" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="C54" t="s">
-        <v>399</v>
+        <v>313</v>
       </c>
       <c r="D54" t="s">
         <v>225</v>
       </c>
       <c r="E54" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="F54" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="B55" t="s">
-        <v>357</v>
+        <v>490</v>
       </c>
       <c r="C55" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="D55" t="s">
         <v>225</v>
       </c>
       <c r="E55" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="F55" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="C56" t="s">
-        <v>274</v>
+        <v>497</v>
       </c>
       <c r="D56" t="s">
         <v>225</v>
       </c>
       <c r="E56" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="F56" t="s">
-        <v>240</v>
+        <v>499</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>513</v>
+        <v>131</v>
       </c>
       <c r="B57" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="C57" t="s">
-        <v>353</v>
+        <v>263</v>
       </c>
       <c r="D57" t="s">
         <v>225</v>
       </c>
       <c r="E57" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="F57" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="B58" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="C58" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="D58" t="s">
         <v>225</v>
       </c>
       <c r="E58" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="F58" t="s">
-        <v>521</v>
+        <v>315</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="B59" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="C59" t="s">
-        <v>525</v>
+        <v>263</v>
       </c>
       <c r="D59" t="s">
         <v>225</v>
       </c>
       <c r="E59" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="F59" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="B60" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="C60" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="D60" t="s">
-        <v>532</v>
+        <v>225</v>
       </c>
       <c r="E60" t="s">
-        <v>276</v>
+        <v>517</v>
       </c>
       <c r="F60" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="B61" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="C61" t="s">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="D61" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E61" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="F61" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="C62" t="s">
-        <v>353</v>
+        <v>528</v>
       </c>
       <c r="D62" t="s">
         <v>225</v>
       </c>
       <c r="E62" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="F62" t="s">
-        <v>276</v>
+        <v>530</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="B63" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="C63" t="s">
-        <v>353</v>
+        <v>534</v>
       </c>
       <c r="D63" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E63" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="F63" t="s">
-        <v>548</v>
+        <v>397</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="B64" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="C64" t="s">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="D64" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E64" t="s">
-        <v>552</v>
+        <v>245</v>
       </c>
       <c r="F64" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="B65" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="C65" t="s">
-        <v>353</v>
+        <v>543</v>
       </c>
       <c r="D65" t="s">
         <v>225</v>
       </c>
       <c r="E65" t="s">
-        <v>276</v>
+        <v>544</v>
       </c>
       <c r="F65" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B66" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="C66" t="s">
-        <v>274</v>
+        <v>549</v>
       </c>
       <c r="D66" t="s">
         <v>225</v>
       </c>
       <c r="E66" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="F66" t="s">
-        <v>562</v>
+        <v>315</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="B67" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="C67" t="s">
-        <v>490</v>
+        <v>313</v>
       </c>
       <c r="D67" t="s">
         <v>225</v>
       </c>
       <c r="E67" t="s">
-        <v>566</v>
+        <v>356</v>
       </c>
       <c r="F67" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="B68" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="C68" t="s">
-        <v>358</v>
+        <v>558</v>
       </c>
       <c r="D68" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E68" t="s">
-        <v>286</v>
+        <v>559</v>
       </c>
       <c r="F68" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="B69" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C69" t="s">
-        <v>333</v>
+        <v>263</v>
       </c>
       <c r="D69" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E69" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="F69" t="s">
-        <v>455</v>
+        <v>565</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="B70" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C70" t="s">
-        <v>244</v>
+        <v>451</v>
       </c>
       <c r="D70" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E70" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="F70" t="s">
-        <v>276</v>
+        <v>570</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B71" t="s">
-        <v>582</v>
+        <v>400</v>
       </c>
       <c r="C71" t="s">
-        <v>274</v>
+        <v>573</v>
       </c>
       <c r="D71" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E71" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="F71" t="s">
-        <v>497</v>
+        <v>575</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B72" t="s">
         <v>578</v>
       </c>
       <c r="C72" t="s">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="D72" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E72" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="F72" t="s">
-        <v>587</v>
+        <v>240</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B73" t="s">
-        <v>489</v>
+        <v>582</v>
       </c>
       <c r="C73" t="s">
-        <v>490</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>225</v>
       </c>
       <c r="E73" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="F73" t="s">
-        <v>492</v>
+        <v>584</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B74" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="C74" t="s">
-        <v>40</v>
+        <v>313</v>
       </c>
       <c r="D74" t="s">
         <v>225</v>
       </c>
       <c r="E74" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="F74" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="B75" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C75" t="s">
-        <v>353</v>
+        <v>593</v>
       </c>
       <c r="D75" t="s">
         <v>225</v>
       </c>
       <c r="E75" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="F75" t="s">
-        <v>276</v>
+        <v>595</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>597</v>
+      </c>
+      <c r="B76" t="s">
+        <v>598</v>
+      </c>
+      <c r="C76" t="s">
+        <v>534</v>
+      </c>
+      <c r="D76" t="s">
+        <v>225</v>
+      </c>
+      <c r="E76" t="s">
+        <v>599</v>
+      </c>
+      <c r="F76" t="s">
+        <v>600</v>
+      </c>
+      <c r="H76" s="2" t="s">
         <v>601</v>
-      </c>
-      <c r="B76" t="s">
-        <v>602</v>
-      </c>
-      <c r="C76" t="s">
-        <v>603</v>
-      </c>
-      <c r="D76" t="s">
-        <v>225</v>
-      </c>
-      <c r="E76" t="s">
-        <v>454</v>
-      </c>
-      <c r="F76" t="s">
-        <v>604</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>602</v>
+      </c>
+      <c r="B77" t="s">
+        <v>603</v>
+      </c>
+      <c r="C77" t="s">
+        <v>604</v>
+      </c>
+      <c r="D77" t="s">
+        <v>309</v>
+      </c>
+      <c r="E77" t="s">
+        <v>315</v>
+      </c>
+      <c r="F77" t="s">
+        <v>605</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="B77" t="s">
-        <v>607</v>
-      </c>
-      <c r="C77" t="s">
-        <v>274</v>
-      </c>
-      <c r="D77" t="s">
-        <v>225</v>
-      </c>
-      <c r="E77" t="s">
-        <v>608</v>
-      </c>
-      <c r="F77" t="s">
-        <v>609</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>607</v>
+      </c>
+      <c r="B78" t="s">
+        <v>608</v>
+      </c>
+      <c r="C78" t="s">
+        <v>609</v>
+      </c>
+      <c r="D78" t="s">
+        <v>257</v>
+      </c>
+      <c r="E78" t="s">
+        <v>610</v>
+      </c>
+      <c r="F78" t="s">
         <v>611</v>
       </c>
-      <c r="B78" t="s">
+      <c r="H78" s="2" t="s">
         <v>612</v>
-      </c>
-      <c r="C78" t="s">
-        <v>613</v>
-      </c>
-      <c r="D78" t="s">
-        <v>225</v>
-      </c>
-      <c r="E78" t="s">
-        <v>614</v>
-      </c>
-      <c r="F78" t="s">
-        <v>615</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B79" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C79" t="s">
-        <v>619</v>
+        <v>263</v>
       </c>
       <c r="D79" t="s">
-        <v>532</v>
+        <v>225</v>
       </c>
       <c r="E79" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="F79" t="s">
-        <v>253</v>
+        <v>315</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B80" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C80" t="s">
-        <v>624</v>
+        <v>263</v>
       </c>
       <c r="D80" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E80" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F80" t="s">
-        <v>276</v>
+        <v>620</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B81" t="s">
-        <v>556</v>
+        <v>623</v>
       </c>
       <c r="C81" t="s">
-        <v>353</v>
+        <v>433</v>
       </c>
       <c r="D81" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E81" t="s">
-        <v>276</v>
+        <v>624</v>
       </c>
       <c r="F81" t="s">
-        <v>557</v>
+        <v>625</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>627</v>
+      </c>
+      <c r="B82" t="s">
+        <v>628</v>
+      </c>
+      <c r="C82" t="s">
+        <v>263</v>
+      </c>
+      <c r="D82" t="s">
+        <v>225</v>
+      </c>
+      <c r="E82" t="s">
+        <v>315</v>
+      </c>
+      <c r="F82" t="s">
         <v>629</v>
       </c>
-      <c r="B82" t="s">
-        <v>623</v>
-      </c>
-      <c r="C82" t="s">
-        <v>624</v>
-      </c>
-      <c r="D82" t="s">
-        <v>225</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="H82" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="F82" t="s">
-        <v>631</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>631</v>
+      </c>
+      <c r="B83" t="s">
+        <v>632</v>
+      </c>
+      <c r="C83" t="s">
+        <v>313</v>
+      </c>
+      <c r="D83" t="s">
+        <v>225</v>
+      </c>
+      <c r="E83" t="s">
         <v>633</v>
       </c>
-      <c r="B83" t="s">
-        <v>480</v>
-      </c>
-      <c r="C83" t="s">
-        <v>481</v>
-      </c>
-      <c r="D83" t="s">
-        <v>225</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>634</v>
-      </c>
-      <c r="F83" t="s">
-        <v>276</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>635</v>
@@ -5673,10 +5904,10 @@
         <v>636</v>
       </c>
       <c r="B84" t="s">
-        <v>276</v>
+        <v>637</v>
       </c>
       <c r="C84" t="s">
-        <v>637</v>
+        <v>558</v>
       </c>
       <c r="D84" t="s">
         <v>225</v>
@@ -5699,16 +5930,16 @@
         <v>642</v>
       </c>
       <c r="C85" t="s">
-        <v>353</v>
+        <v>401</v>
       </c>
       <c r="D85" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E85" t="s">
+        <v>325</v>
+      </c>
+      <c r="F85" t="s">
         <v>643</v>
-      </c>
-      <c r="F85" t="s">
-        <v>276</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>644</v>
@@ -5722,407 +5953,407 @@
         <v>646</v>
       </c>
       <c r="C86" t="s">
+        <v>377</v>
+      </c>
+      <c r="D86" t="s">
+        <v>257</v>
+      </c>
+      <c r="E86" t="s">
         <v>647</v>
       </c>
-      <c r="D86" t="s">
-        <v>225</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
+        <v>524</v>
+      </c>
+      <c r="H86" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="F86" t="s">
-        <v>649</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>649</v>
+      </c>
+      <c r="B87" t="s">
+        <v>650</v>
+      </c>
+      <c r="C87" t="s">
+        <v>250</v>
+      </c>
+      <c r="D87" t="s">
+        <v>257</v>
+      </c>
+      <c r="E87" t="s">
         <v>651</v>
       </c>
-      <c r="B87" t="s">
+      <c r="F87" t="s">
+        <v>315</v>
+      </c>
+      <c r="H87" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="C87" t="s">
-        <v>481</v>
-      </c>
-      <c r="D87" t="s">
-        <v>225</v>
-      </c>
-      <c r="E87" t="s">
-        <v>653</v>
-      </c>
-      <c r="F87" t="s">
-        <v>276</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>653</v>
+      </c>
+      <c r="B88" t="s">
+        <v>654</v>
+      </c>
+      <c r="C88" t="s">
+        <v>313</v>
+      </c>
+      <c r="D88" t="s">
+        <v>257</v>
+      </c>
+      <c r="E88" t="s">
         <v>655</v>
       </c>
-      <c r="B88" t="s">
+      <c r="F88" t="s">
+        <v>565</v>
+      </c>
+      <c r="H88" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="C88" t="s">
-        <v>353</v>
-      </c>
-      <c r="D88" t="s">
-        <v>365</v>
-      </c>
-      <c r="E88" t="s">
-        <v>657</v>
-      </c>
-      <c r="F88" t="s">
-        <v>658</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>657</v>
+      </c>
+      <c r="B89" t="s">
+        <v>650</v>
+      </c>
+      <c r="C89" t="s">
+        <v>250</v>
+      </c>
+      <c r="D89" t="s">
+        <v>257</v>
+      </c>
+      <c r="E89" t="s">
+        <v>658</v>
+      </c>
+      <c r="F89" t="s">
+        <v>659</v>
+      </c>
+      <c r="H89" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="B89" t="s">
-        <v>661</v>
-      </c>
-      <c r="C89" t="s">
-        <v>353</v>
-      </c>
-      <c r="D89" t="s">
-        <v>225</v>
-      </c>
-      <c r="E89" t="s">
-        <v>662</v>
-      </c>
-      <c r="F89" t="s">
-        <v>663</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B90" t="s">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="C90" t="s">
-        <v>274</v>
+        <v>558</v>
       </c>
       <c r="D90" t="s">
         <v>225</v>
       </c>
       <c r="E90" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="F90" t="s">
-        <v>667</v>
+        <v>560</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B91" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C91" t="s">
-        <v>671</v>
+        <v>40</v>
       </c>
       <c r="D91" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E91" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="F91" t="s">
-        <v>276</v>
+        <v>667</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B92" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="C92" t="s">
-        <v>676</v>
+        <v>263</v>
       </c>
       <c r="D92" t="s">
         <v>225</v>
       </c>
       <c r="E92" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="F92" t="s">
-        <v>678</v>
+        <v>315</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="B93" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="C93" t="s">
-        <v>307</v>
+        <v>675</v>
       </c>
       <c r="D93" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="E93" t="s">
-        <v>682</v>
+        <v>523</v>
       </c>
       <c r="F93" t="s">
-        <v>486</v>
+        <v>676</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="B94" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="C94" t="s">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="D94" t="s">
         <v>225</v>
       </c>
       <c r="E94" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="F94" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B95" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C95" t="s">
-        <v>353</v>
+        <v>685</v>
       </c>
       <c r="D95" t="s">
         <v>225</v>
       </c>
       <c r="E95" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="F95" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="B96" t="s">
-        <v>519</v>
+        <v>690</v>
       </c>
       <c r="C96" t="s">
-        <v>274</v>
+        <v>691</v>
       </c>
       <c r="D96" t="s">
-        <v>225</v>
+        <v>309</v>
       </c>
       <c r="E96" t="s">
-        <v>695</v>
+        <v>415</v>
       </c>
       <c r="F96" t="s">
-        <v>696</v>
+        <v>259</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="B97" t="s">
-        <v>338</v>
+        <v>694</v>
       </c>
       <c r="C97" t="s">
-        <v>339</v>
+        <v>695</v>
       </c>
       <c r="D97" t="s">
         <v>225</v>
       </c>
       <c r="E97" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="F97" t="s">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B98" t="s">
-        <v>338</v>
+        <v>628</v>
       </c>
       <c r="C98" t="s">
-        <v>339</v>
+        <v>263</v>
       </c>
       <c r="D98" t="s">
         <v>225</v>
       </c>
       <c r="E98" t="s">
-        <v>702</v>
+        <v>315</v>
       </c>
       <c r="F98" t="s">
-        <v>227</v>
+        <v>629</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B99" t="s">
-        <v>480</v>
+        <v>694</v>
       </c>
       <c r="C99" t="s">
-        <v>481</v>
+        <v>695</v>
       </c>
       <c r="D99" t="s">
         <v>225</v>
       </c>
       <c r="E99" t="s">
-        <v>608</v>
+        <v>701</v>
       </c>
       <c r="F99" t="s">
-        <v>276</v>
+        <v>702</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>704</v>
+      </c>
+      <c r="B100" t="s">
+        <v>548</v>
+      </c>
+      <c r="C100" t="s">
+        <v>549</v>
+      </c>
+      <c r="D100" t="s">
+        <v>225</v>
+      </c>
+      <c r="E100" t="s">
+        <v>705</v>
+      </c>
+      <c r="F100" t="s">
+        <v>315</v>
+      </c>
+      <c r="H100" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="B100" t="s">
-        <v>338</v>
-      </c>
-      <c r="C100" t="s">
-        <v>339</v>
-      </c>
-      <c r="D100" t="s">
-        <v>225</v>
-      </c>
-      <c r="E100" t="s">
-        <v>707</v>
-      </c>
-      <c r="F100" t="s">
-        <v>227</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>707</v>
+      </c>
+      <c r="B101" t="s">
+        <v>315</v>
+      </c>
+      <c r="C101" t="s">
+        <v>708</v>
+      </c>
+      <c r="D101" t="s">
+        <v>225</v>
+      </c>
+      <c r="E101" t="s">
         <v>709</v>
       </c>
-      <c r="B101" t="s">
+      <c r="F101" t="s">
         <v>710</v>
       </c>
-      <c r="C101" t="s">
-        <v>353</v>
-      </c>
-      <c r="D101" t="s">
-        <v>225</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="H101" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="F101" t="s">
-        <v>276</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>712</v>
+      </c>
+      <c r="B102" t="s">
         <v>713</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
+        <v>263</v>
+      </c>
+      <c r="D102" t="s">
+        <v>225</v>
+      </c>
+      <c r="E102" t="s">
         <v>714</v>
       </c>
-      <c r="C102" t="s">
+      <c r="F102" t="s">
+        <v>315</v>
+      </c>
+      <c r="H102" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="D102" t="s">
-        <v>365</v>
-      </c>
-      <c r="E102" t="s">
-        <v>716</v>
-      </c>
-      <c r="F102" t="s">
-        <v>717</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>716</v>
+      </c>
+      <c r="B103" t="s">
+        <v>717</v>
+      </c>
+      <c r="C103" t="s">
+        <v>718</v>
+      </c>
+      <c r="D103" t="s">
+        <v>225</v>
+      </c>
+      <c r="E103" t="s">
         <v>719</v>
       </c>
-      <c r="B103" t="s">
-        <v>410</v>
-      </c>
-      <c r="C103" t="s">
-        <v>274</v>
-      </c>
-      <c r="D103" t="s">
-        <v>225</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>720</v>
-      </c>
-      <c r="F103" t="s">
-        <v>276</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>721</v>
@@ -6136,7 +6367,7 @@
         <v>723</v>
       </c>
       <c r="C104" t="s">
-        <v>244</v>
+        <v>549</v>
       </c>
       <c r="D104" t="s">
         <v>225</v>
@@ -6145,7 +6376,7 @@
         <v>724</v>
       </c>
       <c r="F104" t="s">
-        <v>507</v>
+        <v>315</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>725</v>
@@ -6159,19 +6390,456 @@
         <v>727</v>
       </c>
       <c r="C105" t="s">
-        <v>364</v>
+        <v>263</v>
       </c>
       <c r="D105" t="s">
-        <v>225</v>
+        <v>408</v>
       </c>
       <c r="E105" t="s">
         <v>728</v>
       </c>
       <c r="F105" t="s">
-        <v>276</v>
+        <v>729</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>731</v>
+      </c>
+      <c r="B106" t="s">
+        <v>732</v>
+      </c>
+      <c r="C106" t="s">
+        <v>263</v>
+      </c>
+      <c r="D106" t="s">
+        <v>225</v>
+      </c>
+      <c r="E106" t="s">
+        <v>733</v>
+      </c>
+      <c r="F106" t="s">
+        <v>734</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>736</v>
+      </c>
+      <c r="B107" t="s">
+        <v>587</v>
+      </c>
+      <c r="C107" t="s">
+        <v>313</v>
+      </c>
+      <c r="D107" t="s">
+        <v>225</v>
+      </c>
+      <c r="E107" t="s">
+        <v>737</v>
+      </c>
+      <c r="F107" t="s">
+        <v>738</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>740</v>
+      </c>
+      <c r="B108" t="s">
+        <v>741</v>
+      </c>
+      <c r="C108" t="s">
+        <v>742</v>
+      </c>
+      <c r="D108" t="s">
+        <v>257</v>
+      </c>
+      <c r="E108" t="s">
+        <v>743</v>
+      </c>
+      <c r="F108" t="s">
+        <v>315</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>745</v>
+      </c>
+      <c r="B109" t="s">
+        <v>746</v>
+      </c>
+      <c r="C109" t="s">
+        <v>303</v>
+      </c>
+      <c r="D109" t="s">
+        <v>225</v>
+      </c>
+      <c r="E109" t="s">
+        <v>747</v>
+      </c>
+      <c r="F109" t="s">
+        <v>748</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>750</v>
+      </c>
+      <c r="B110" t="s">
+        <v>751</v>
+      </c>
+      <c r="C110" t="s">
+        <v>351</v>
+      </c>
+      <c r="D110" t="s">
+        <v>257</v>
+      </c>
+      <c r="E110" t="s">
+        <v>752</v>
+      </c>
+      <c r="F110" t="s">
+        <v>554</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>754</v>
+      </c>
+      <c r="B111" t="s">
+        <v>755</v>
+      </c>
+      <c r="C111" t="s">
+        <v>263</v>
+      </c>
+      <c r="D111" t="s">
+        <v>225</v>
+      </c>
+      <c r="E111" t="s">
+        <v>756</v>
+      </c>
+      <c r="F111" t="s">
+        <v>757</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>759</v>
+      </c>
+      <c r="B112" t="s">
+        <v>760</v>
+      </c>
+      <c r="C112" t="s">
+        <v>263</v>
+      </c>
+      <c r="D112" t="s">
+        <v>225</v>
+      </c>
+      <c r="E112" t="s">
+        <v>761</v>
+      </c>
+      <c r="F112" t="s">
+        <v>762</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>764</v>
+      </c>
+      <c r="B113" t="s">
+        <v>587</v>
+      </c>
+      <c r="C113" t="s">
+        <v>313</v>
+      </c>
+      <c r="D113" t="s">
+        <v>225</v>
+      </c>
+      <c r="E113" t="s">
+        <v>765</v>
+      </c>
+      <c r="F113" t="s">
+        <v>766</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>768</v>
+      </c>
+      <c r="B114" t="s">
+        <v>382</v>
+      </c>
+      <c r="C114" t="s">
+        <v>383</v>
+      </c>
+      <c r="D114" t="s">
+        <v>225</v>
+      </c>
+      <c r="E114" t="s">
+        <v>769</v>
+      </c>
+      <c r="F114" t="s">
+        <v>227</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>771</v>
+      </c>
+      <c r="B115" t="s">
+        <v>382</v>
+      </c>
+      <c r="C115" t="s">
+        <v>383</v>
+      </c>
+      <c r="D115" t="s">
+        <v>225</v>
+      </c>
+      <c r="E115" t="s">
+        <v>772</v>
+      </c>
+      <c r="F115" t="s">
+        <v>227</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>774</v>
+      </c>
+      <c r="B116" t="s">
+        <v>548</v>
+      </c>
+      <c r="C116" t="s">
+        <v>549</v>
+      </c>
+      <c r="D116" t="s">
+        <v>225</v>
+      </c>
+      <c r="E116" t="s">
+        <v>680</v>
+      </c>
+      <c r="F116" t="s">
+        <v>315</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>776</v>
+      </c>
+      <c r="B117" t="s">
+        <v>290</v>
+      </c>
+      <c r="C117" t="s">
+        <v>303</v>
+      </c>
+      <c r="D117" t="s">
+        <v>309</v>
+      </c>
+      <c r="E117" t="s">
+        <v>777</v>
+      </c>
+      <c r="F117" t="s">
+        <v>293</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>779</v>
+      </c>
+      <c r="B118" t="s">
+        <v>382</v>
+      </c>
+      <c r="C118" t="s">
+        <v>383</v>
+      </c>
+      <c r="D118" t="s">
+        <v>225</v>
+      </c>
+      <c r="E118" t="s">
+        <v>780</v>
+      </c>
+      <c r="F118" t="s">
+        <v>227</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>782</v>
+      </c>
+      <c r="B119" t="s">
+        <v>783</v>
+      </c>
+      <c r="C119" t="s">
+        <v>263</v>
+      </c>
+      <c r="D119" t="s">
+        <v>225</v>
+      </c>
+      <c r="E119" t="s">
+        <v>784</v>
+      </c>
+      <c r="F119" t="s">
+        <v>315</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>786</v>
+      </c>
+      <c r="B120" t="s">
+        <v>787</v>
+      </c>
+      <c r="C120" t="s">
+        <v>788</v>
+      </c>
+      <c r="D120" t="s">
+        <v>225</v>
+      </c>
+      <c r="E120" t="s">
+        <v>789</v>
+      </c>
+      <c r="F120" t="s">
+        <v>315</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>791</v>
+      </c>
+      <c r="B121" t="s">
+        <v>792</v>
+      </c>
+      <c r="C121" t="s">
+        <v>793</v>
+      </c>
+      <c r="D121" t="s">
+        <v>408</v>
+      </c>
+      <c r="E121" t="s">
+        <v>794</v>
+      </c>
+      <c r="F121" t="s">
+        <v>293</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>796</v>
+      </c>
+      <c r="B122" t="s">
+        <v>470</v>
+      </c>
+      <c r="C122" t="s">
+        <v>313</v>
+      </c>
+      <c r="D122" t="s">
+        <v>225</v>
+      </c>
+      <c r="E122" t="s">
+        <v>797</v>
+      </c>
+      <c r="F122" t="s">
+        <v>315</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>799</v>
+      </c>
+      <c r="B123" t="s">
+        <v>800</v>
+      </c>
+      <c r="C123" t="s">
+        <v>250</v>
+      </c>
+      <c r="D123" t="s">
+        <v>225</v>
+      </c>
+      <c r="E123" t="s">
+        <v>801</v>
+      </c>
+      <c r="F123" t="s">
+        <v>575</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>803</v>
+      </c>
+      <c r="B124" t="s">
+        <v>804</v>
+      </c>
+      <c r="C124" t="s">
+        <v>407</v>
+      </c>
+      <c r="D124" t="s">
+        <v>225</v>
+      </c>
+      <c r="E124" t="s">
+        <v>805</v>
+      </c>
+      <c r="F124" t="s">
+        <v>315</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>806</v>
       </c>
     </row>
   </sheetData>
@@ -6281,6 +6949,25 @@
     <hyperlink ref="H103" r:id="rId102"/>
     <hyperlink ref="H104" r:id="rId103"/>
     <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-10-05.xlsx
+++ b/docs/xlsx/jobs-2026-10-05.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="818">
   <si>
     <t>Title</t>
   </si>
@@ -1189,6 +1189,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0f8ef73a3a314bc7814aa5857753da76-community-conservation-senior-manager-panthera-kafue</t>
   </si>
   <si>
+    <t>Community Loan Officer</t>
+  </si>
+  <si>
+    <t>Women's Opportunities Resource Center</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>USD 50.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80c17dcdc82c40d9b4f450ff8c532d4d-community-loan-officer-womens-opportunities-resource-center-philadelphia</t>
+  </si>
+  <si>
     <t>Community Organizer</t>
   </si>
   <si>
@@ -1216,9 +1234,6 @@
     <t>Contract Compliance and Impact Specialist or Analyst</t>
   </si>
   <si>
-    <t>Women's Opportunities Resource Center</t>
-  </si>
-  <si>
     <t>Philadelphia, Pennsylvania</t>
   </si>
   <si>
@@ -1327,6 +1342,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/4c847750ae6540b894843195202528fb-development-coordinator-friendshipworks-inc-boston</t>
   </si>
   <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>The Haven MN</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c35f418e893475e95dbf484464c4eff-development-director-the-haven-mn-minneapolis</t>
+  </si>
+  <si>
     <t>Digital Communications Coordinator</t>
   </si>
   <si>
@@ -1735,15 +1768,9 @@
     <t>Loan Administrator</t>
   </si>
   <si>
-    <t>Philadelphia, PA</t>
-  </si>
-  <si>
     <t>USD 65000.00/year</t>
   </si>
   <si>
-    <t>Community Development, Economic Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/80c17dcdc82c40d9b4f450ff8c532d4d-loan-administrator-womens-opportunities-resource-center-philadelphia</t>
   </si>
   <si>
@@ -2372,6 +2399,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/business-job/8650e7ff06dc4963a92ac1d6d319d371-systems-change-policy-strategy-manager-rebel-heart-therapy-portland</t>
+  </si>
+  <si>
+    <t>RDI - Rural Development Initiatives</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/8650e7ff06dc4963a92ac1d6d319d371-systems-change-policy-strategy-manager-rdi-rural-development-initiatives-portland</t>
   </si>
   <si>
     <t>Technology Coordinator, NASS Program</t>
@@ -3974,7 +4007,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4777,62 +4810,62 @@
         <v>391</v>
       </c>
       <c r="B35" t="s">
-        <v>312</v>
+        <v>392</v>
       </c>
       <c r="C35" t="s">
-        <v>313</v>
+        <v>393</v>
       </c>
       <c r="D35" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="E35" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F35" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B36" t="s">
-        <v>396</v>
+        <v>312</v>
       </c>
       <c r="C36" t="s">
-        <v>263</v>
+        <v>313</v>
       </c>
       <c r="D36" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E36" t="s">
-        <v>315</v>
+        <v>398</v>
       </c>
       <c r="F36" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B37" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C37" t="s">
-        <v>401</v>
+        <v>263</v>
       </c>
       <c r="D37" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="E37" t="s">
-        <v>402</v>
+        <v>315</v>
       </c>
       <c r="F37" t="s">
         <v>403</v>
@@ -4846,56 +4879,56 @@
         <v>405</v>
       </c>
       <c r="B38" t="s">
+        <v>392</v>
+      </c>
+      <c r="C38" t="s">
         <v>406</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>257</v>
+      </c>
+      <c r="E38" t="s">
         <v>407</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>408</v>
       </c>
-      <c r="E38" t="s">
+      <c r="H38" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="F38" t="s">
-        <v>410</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>410</v>
+      </c>
+      <c r="B39" t="s">
+        <v>411</v>
+      </c>
+      <c r="C39" t="s">
         <v>412</v>
       </c>
-      <c r="B39" t="s">
+      <c r="D39" t="s">
         <v>413</v>
       </c>
-      <c r="C39" t="s">
+      <c r="E39" t="s">
         <v>414</v>
       </c>
-      <c r="D39" t="s">
-        <v>225</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>415</v>
       </c>
-      <c r="F39" t="s">
+      <c r="H39" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>417</v>
+      </c>
+      <c r="B40" t="s">
         <v>418</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>419</v>
-      </c>
-      <c r="C40" t="s">
-        <v>313</v>
       </c>
       <c r="D40" t="s">
         <v>225</v>
@@ -4918,16 +4951,16 @@
         <v>424</v>
       </c>
       <c r="C41" t="s">
+        <v>313</v>
+      </c>
+      <c r="D41" t="s">
+        <v>225</v>
+      </c>
+      <c r="E41" t="s">
         <v>425</v>
       </c>
-      <c r="D41" t="s">
-        <v>225</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>426</v>
-      </c>
-      <c r="F41" t="s">
-        <v>315</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>427</v>
@@ -4938,33 +4971,33 @@
         <v>428</v>
       </c>
       <c r="B42" t="s">
-        <v>382</v>
+        <v>429</v>
       </c>
       <c r="C42" t="s">
-        <v>383</v>
+        <v>430</v>
       </c>
       <c r="D42" t="s">
         <v>225</v>
       </c>
       <c r="E42" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F42" t="s">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B43" t="s">
-        <v>432</v>
+        <v>382</v>
       </c>
       <c r="C43" t="s">
-        <v>433</v>
+        <v>383</v>
       </c>
       <c r="D43" t="s">
         <v>225</v>
@@ -4973,21 +5006,21 @@
         <v>434</v>
       </c>
       <c r="F43" t="s">
+        <v>227</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>436</v>
+      </c>
+      <c r="B44" t="s">
         <v>437</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>438</v>
-      </c>
-      <c r="C44" t="s">
-        <v>263</v>
       </c>
       <c r="D44" t="s">
         <v>225</v>
@@ -5010,70 +5043,70 @@
         <v>443</v>
       </c>
       <c r="C45" t="s">
-        <v>313</v>
+        <v>444</v>
       </c>
       <c r="D45" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E45" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F45" t="s">
-        <v>315</v>
+        <v>446</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B46" t="s">
-        <v>290</v>
+        <v>449</v>
       </c>
       <c r="C46" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="D46" t="s">
         <v>225</v>
       </c>
       <c r="E46" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F46" t="s">
-        <v>293</v>
+        <v>451</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B47" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C47" t="s">
-        <v>451</v>
+        <v>313</v>
       </c>
       <c r="D47" t="s">
         <v>225</v>
       </c>
       <c r="E47" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F47" t="s">
-        <v>453</v>
+        <v>315</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s">
         <v>290</v>
@@ -5085,56 +5118,56 @@
         <v>225</v>
       </c>
       <c r="E48" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F48" t="s">
-        <v>240</v>
+        <v>293</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D49" t="s">
         <v>225</v>
       </c>
       <c r="E49" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F49" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B50" t="s">
-        <v>465</v>
+        <v>290</v>
       </c>
       <c r="C50" t="s">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="D50" t="s">
         <v>225</v>
       </c>
       <c r="E50" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F50" t="s">
-        <v>467</v>
+        <v>240</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>468</v>
@@ -5148,62 +5181,62 @@
         <v>470</v>
       </c>
       <c r="C51" t="s">
-        <v>313</v>
+        <v>471</v>
       </c>
       <c r="D51" t="s">
         <v>225</v>
       </c>
       <c r="E51" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F51" t="s">
-        <v>315</v>
+        <v>473</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B52" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C52" t="s">
-        <v>475</v>
+        <v>351</v>
       </c>
       <c r="D52" t="s">
         <v>225</v>
       </c>
       <c r="E52" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F52" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C53" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="D53" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="E53" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F53" t="s">
-        <v>482</v>
+        <v>315</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>483</v>
@@ -5217,33 +5250,33 @@
         <v>485</v>
       </c>
       <c r="C54" t="s">
-        <v>313</v>
+        <v>486</v>
       </c>
       <c r="D54" t="s">
         <v>225</v>
       </c>
       <c r="E54" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F54" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B55" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C55" t="s">
-        <v>491</v>
+        <v>303</v>
       </c>
       <c r="D55" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E55" t="s">
         <v>492</v>
@@ -5263,73 +5296,73 @@
         <v>496</v>
       </c>
       <c r="C56" t="s">
+        <v>313</v>
+      </c>
+      <c r="D56" t="s">
+        <v>225</v>
+      </c>
+      <c r="E56" t="s">
         <v>497</v>
       </c>
-      <c r="D56" t="s">
-        <v>225</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>498</v>
       </c>
-      <c r="F56" t="s">
+      <c r="H56" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>500</v>
       </c>
       <c r="B57" t="s">
         <v>501</v>
       </c>
       <c r="C57" t="s">
-        <v>263</v>
+        <v>502</v>
       </c>
       <c r="D57" t="s">
         <v>225</v>
       </c>
       <c r="E57" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F57" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C58" t="s">
-        <v>256</v>
+        <v>508</v>
       </c>
       <c r="D58" t="s">
         <v>225</v>
       </c>
       <c r="E58" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F58" t="s">
-        <v>315</v>
+        <v>510</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>509</v>
+        <v>131</v>
       </c>
       <c r="B59" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C59" t="s">
         <v>263</v>
@@ -5338,33 +5371,33 @@
         <v>225</v>
       </c>
       <c r="E59" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F59" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B60" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C60" t="s">
-        <v>516</v>
+        <v>256</v>
       </c>
       <c r="D60" t="s">
         <v>225</v>
       </c>
       <c r="E60" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F60" t="s">
-        <v>518</v>
+        <v>315</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>519</v>
@@ -5378,62 +5411,62 @@
         <v>521</v>
       </c>
       <c r="C61" t="s">
+        <v>263</v>
+      </c>
+      <c r="D61" t="s">
+        <v>225</v>
+      </c>
+      <c r="E61" t="s">
         <v>522</v>
       </c>
-      <c r="D61" t="s">
-        <v>257</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>523</v>
       </c>
-      <c r="F61" t="s">
+      <c r="H61" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>525</v>
+      </c>
+      <c r="B62" t="s">
         <v>526</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>527</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
+        <v>225</v>
+      </c>
+      <c r="E62" t="s">
         <v>528</v>
       </c>
-      <c r="D62" t="s">
-        <v>225</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>529</v>
       </c>
-      <c r="F62" t="s">
+      <c r="H62" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>531</v>
+      </c>
+      <c r="B63" t="s">
         <v>532</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>533</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>257</v>
+      </c>
+      <c r="E63" t="s">
         <v>534</v>
       </c>
-      <c r="D63" t="s">
-        <v>225</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>535</v>
-      </c>
-      <c r="F63" t="s">
-        <v>397</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>536</v>
@@ -5447,62 +5480,62 @@
         <v>538</v>
       </c>
       <c r="C64" t="s">
-        <v>250</v>
+        <v>539</v>
       </c>
       <c r="D64" t="s">
         <v>225</v>
       </c>
       <c r="E64" t="s">
-        <v>245</v>
+        <v>540</v>
       </c>
       <c r="F64" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B65" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C65" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D65" t="s">
         <v>225</v>
       </c>
       <c r="E65" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F65" t="s">
-        <v>545</v>
+        <v>403</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B66" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C66" t="s">
-        <v>549</v>
+        <v>250</v>
       </c>
       <c r="D66" t="s">
         <v>225</v>
       </c>
       <c r="E66" t="s">
+        <v>245</v>
+      </c>
+      <c r="F66" t="s">
         <v>550</v>
-      </c>
-      <c r="F66" t="s">
-        <v>315</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>551</v>
@@ -5516,59 +5549,59 @@
         <v>553</v>
       </c>
       <c r="C67" t="s">
-        <v>313</v>
+        <v>554</v>
       </c>
       <c r="D67" t="s">
         <v>225</v>
       </c>
       <c r="E67" t="s">
-        <v>356</v>
+        <v>555</v>
       </c>
       <c r="F67" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B68" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C68" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D68" t="s">
         <v>225</v>
       </c>
       <c r="E68" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F68" t="s">
-        <v>560</v>
+        <v>315</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B69" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C69" t="s">
-        <v>263</v>
+        <v>313</v>
       </c>
       <c r="D69" t="s">
         <v>225</v>
       </c>
       <c r="E69" t="s">
-        <v>564</v>
+        <v>356</v>
       </c>
       <c r="F69" t="s">
         <v>565</v>
@@ -5585,85 +5618,85 @@
         <v>568</v>
       </c>
       <c r="C70" t="s">
-        <v>451</v>
+        <v>569</v>
       </c>
       <c r="D70" t="s">
         <v>225</v>
       </c>
       <c r="E70" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F70" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B71" t="s">
-        <v>400</v>
+        <v>574</v>
       </c>
       <c r="C71" t="s">
-        <v>573</v>
+        <v>263</v>
       </c>
       <c r="D71" t="s">
         <v>225</v>
       </c>
       <c r="E71" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F71" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B72" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C72" t="s">
-        <v>313</v>
+        <v>462</v>
       </c>
       <c r="D72" t="s">
         <v>225</v>
       </c>
       <c r="E72" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F72" t="s">
-        <v>240</v>
+        <v>581</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B73" t="s">
-        <v>582</v>
+        <v>392</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>393</v>
       </c>
       <c r="D73" t="s">
         <v>225</v>
       </c>
       <c r="E73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F73" t="s">
-        <v>584</v>
+        <v>395</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>585</v>
@@ -5686,136 +5719,136 @@
         <v>588</v>
       </c>
       <c r="F74" t="s">
+        <v>240</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>590</v>
+      </c>
+      <c r="B75" t="s">
         <v>591</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
+        <v>263</v>
+      </c>
+      <c r="D75" t="s">
+        <v>225</v>
+      </c>
+      <c r="E75" t="s">
         <v>592</v>
       </c>
-      <c r="C75" t="s">
+      <c r="F75" t="s">
         <v>593</v>
       </c>
-      <c r="D75" t="s">
-        <v>225</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="H75" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="F75" t="s">
-        <v>595</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>595</v>
+      </c>
+      <c r="B76" t="s">
+        <v>596</v>
+      </c>
+      <c r="C76" t="s">
+        <v>313</v>
+      </c>
+      <c r="D76" t="s">
+        <v>225</v>
+      </c>
+      <c r="E76" t="s">
         <v>597</v>
       </c>
-      <c r="B76" t="s">
+      <c r="F76" t="s">
         <v>598</v>
       </c>
-      <c r="C76" t="s">
-        <v>534</v>
-      </c>
-      <c r="D76" t="s">
-        <v>225</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="H76" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="F76" t="s">
-        <v>600</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>600</v>
+      </c>
+      <c r="B77" t="s">
+        <v>601</v>
+      </c>
+      <c r="C77" t="s">
         <v>602</v>
       </c>
-      <c r="B77" t="s">
+      <c r="D77" t="s">
+        <v>225</v>
+      </c>
+      <c r="E77" t="s">
         <v>603</v>
       </c>
-      <c r="C77" t="s">
+      <c r="F77" t="s">
         <v>604</v>
       </c>
-      <c r="D77" t="s">
-        <v>309</v>
-      </c>
-      <c r="E77" t="s">
-        <v>315</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="H77" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>606</v>
+      </c>
+      <c r="B78" t="s">
         <v>607</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
+        <v>545</v>
+      </c>
+      <c r="D78" t="s">
+        <v>225</v>
+      </c>
+      <c r="E78" t="s">
         <v>608</v>
       </c>
-      <c r="C78" t="s">
+      <c r="F78" t="s">
         <v>609</v>
       </c>
-      <c r="D78" t="s">
-        <v>257</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="H78" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="F78" t="s">
-        <v>611</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>611</v>
+      </c>
+      <c r="B79" t="s">
+        <v>612</v>
+      </c>
+      <c r="C79" t="s">
         <v>613</v>
       </c>
-      <c r="B79" t="s">
+      <c r="D79" t="s">
+        <v>309</v>
+      </c>
+      <c r="E79" t="s">
+        <v>315</v>
+      </c>
+      <c r="F79" t="s">
         <v>614</v>
       </c>
-      <c r="C79" t="s">
-        <v>263</v>
-      </c>
-      <c r="D79" t="s">
-        <v>225</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="H79" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="F79" t="s">
-        <v>315</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>616</v>
+      </c>
+      <c r="B80" t="s">
         <v>617</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>618</v>
-      </c>
-      <c r="C80" t="s">
-        <v>263</v>
       </c>
       <c r="D80" t="s">
         <v>257</v>
@@ -5838,36 +5871,36 @@
         <v>623</v>
       </c>
       <c r="C81" t="s">
-        <v>433</v>
+        <v>263</v>
       </c>
       <c r="D81" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="E81" t="s">
         <v>624</v>
       </c>
       <c r="F81" t="s">
+        <v>315</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>626</v>
+      </c>
+      <c r="B82" t="s">
         <v>627</v>
-      </c>
-      <c r="B82" t="s">
-        <v>628</v>
       </c>
       <c r="C82" t="s">
         <v>263</v>
       </c>
       <c r="D82" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E82" t="s">
-        <v>315</v>
+        <v>628</v>
       </c>
       <c r="F82" t="s">
         <v>629</v>
@@ -5884,10 +5917,10 @@
         <v>632</v>
       </c>
       <c r="C83" t="s">
-        <v>313</v>
+        <v>438</v>
       </c>
       <c r="D83" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E83" t="s">
         <v>633</v>
@@ -5907,36 +5940,36 @@
         <v>637</v>
       </c>
       <c r="C84" t="s">
-        <v>558</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>225</v>
       </c>
       <c r="E84" t="s">
+        <v>315</v>
+      </c>
+      <c r="F84" t="s">
         <v>638</v>
       </c>
-      <c r="F84" t="s">
+      <c r="H84" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>640</v>
+      </c>
+      <c r="B85" t="s">
         <v>641</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
+        <v>313</v>
+      </c>
+      <c r="D85" t="s">
+        <v>225</v>
+      </c>
+      <c r="E85" t="s">
         <v>642</v>
-      </c>
-      <c r="C85" t="s">
-        <v>401</v>
-      </c>
-      <c r="D85" t="s">
-        <v>257</v>
-      </c>
-      <c r="E85" t="s">
-        <v>325</v>
       </c>
       <c r="F85" t="s">
         <v>643</v>
@@ -5953,73 +5986,73 @@
         <v>646</v>
       </c>
       <c r="C86" t="s">
-        <v>377</v>
+        <v>569</v>
       </c>
       <c r="D86" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="E86" t="s">
         <v>647</v>
       </c>
       <c r="F86" t="s">
-        <v>524</v>
+        <v>648</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B87" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C87" t="s">
-        <v>250</v>
+        <v>406</v>
       </c>
       <c r="D87" t="s">
         <v>257</v>
       </c>
       <c r="E87" t="s">
-        <v>651</v>
+        <v>325</v>
       </c>
       <c r="F87" t="s">
-        <v>315</v>
+        <v>652</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B88" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C88" t="s">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="D88" t="s">
         <v>257</v>
       </c>
       <c r="E88" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F88" t="s">
-        <v>565</v>
+        <v>535</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B89" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="C89" t="s">
         <v>250</v>
@@ -6028,70 +6061,70 @@
         <v>257</v>
       </c>
       <c r="E89" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F89" t="s">
-        <v>659</v>
+        <v>315</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B90" t="s">
-        <v>557</v>
+        <v>663</v>
       </c>
       <c r="C90" t="s">
-        <v>558</v>
+        <v>313</v>
       </c>
       <c r="D90" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E90" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F90" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B91" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="C91" t="s">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="D91" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E91" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F91" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B92" t="s">
-        <v>670</v>
+        <v>568</v>
       </c>
       <c r="C92" t="s">
-        <v>263</v>
+        <v>569</v>
       </c>
       <c r="D92" t="s">
         <v>225</v>
@@ -6100,7 +6133,7 @@
         <v>671</v>
       </c>
       <c r="F92" t="s">
-        <v>315</v>
+        <v>571</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>672</v>
@@ -6114,13 +6147,13 @@
         <v>674</v>
       </c>
       <c r="C93" t="s">
+        <v>40</v>
+      </c>
+      <c r="D93" t="s">
+        <v>225</v>
+      </c>
+      <c r="E93" t="s">
         <v>675</v>
-      </c>
-      <c r="D93" t="s">
-        <v>225</v>
-      </c>
-      <c r="E93" t="s">
-        <v>523</v>
       </c>
       <c r="F93" t="s">
         <v>676</v>
@@ -6137,7 +6170,7 @@
         <v>679</v>
       </c>
       <c r="C94" t="s">
-        <v>313</v>
+        <v>263</v>
       </c>
       <c r="D94" t="s">
         <v>225</v>
@@ -6146,76 +6179,76 @@
         <v>680</v>
       </c>
       <c r="F94" t="s">
+        <v>315</v>
+      </c>
+      <c r="H94" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>682</v>
+      </c>
+      <c r="B95" t="s">
         <v>683</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>684</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
+        <v>225</v>
+      </c>
+      <c r="E95" t="s">
+        <v>534</v>
+      </c>
+      <c r="F95" t="s">
         <v>685</v>
       </c>
-      <c r="D95" t="s">
-        <v>225</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="H95" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="F95" t="s">
-        <v>687</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>687</v>
+      </c>
+      <c r="B96" t="s">
+        <v>688</v>
+      </c>
+      <c r="C96" t="s">
+        <v>313</v>
+      </c>
+      <c r="D96" t="s">
+        <v>225</v>
+      </c>
+      <c r="E96" t="s">
         <v>689</v>
       </c>
-      <c r="B96" t="s">
+      <c r="F96" t="s">
         <v>690</v>
       </c>
-      <c r="C96" t="s">
+      <c r="H96" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="D96" t="s">
-        <v>309</v>
-      </c>
-      <c r="E96" t="s">
-        <v>415</v>
-      </c>
-      <c r="F96" t="s">
-        <v>259</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>692</v>
+      </c>
+      <c r="B97" t="s">
         <v>693</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>694</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
+        <v>225</v>
+      </c>
+      <c r="E97" t="s">
         <v>695</v>
       </c>
-      <c r="D97" t="s">
-        <v>225</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>696</v>
-      </c>
-      <c r="F97" t="s">
-        <v>315</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>697</v>
@@ -6226,102 +6259,102 @@
         <v>698</v>
       </c>
       <c r="B98" t="s">
-        <v>628</v>
+        <v>699</v>
       </c>
       <c r="C98" t="s">
-        <v>263</v>
+        <v>700</v>
       </c>
       <c r="D98" t="s">
-        <v>225</v>
+        <v>309</v>
       </c>
       <c r="E98" t="s">
-        <v>315</v>
+        <v>420</v>
       </c>
       <c r="F98" t="s">
-        <v>629</v>
+        <v>259</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B99" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="C99" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="D99" t="s">
         <v>225</v>
       </c>
       <c r="E99" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="F99" t="s">
-        <v>702</v>
+        <v>315</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B100" t="s">
-        <v>548</v>
+        <v>637</v>
       </c>
       <c r="C100" t="s">
-        <v>549</v>
+        <v>263</v>
       </c>
       <c r="D100" t="s">
         <v>225</v>
       </c>
       <c r="E100" t="s">
-        <v>705</v>
+        <v>315</v>
       </c>
       <c r="F100" t="s">
-        <v>315</v>
+        <v>638</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B101" t="s">
-        <v>315</v>
+        <v>703</v>
       </c>
       <c r="C101" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="D101" t="s">
         <v>225</v>
       </c>
       <c r="E101" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F101" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B102" t="s">
-        <v>713</v>
+        <v>559</v>
       </c>
       <c r="C102" t="s">
-        <v>263</v>
+        <v>560</v>
       </c>
       <c r="D102" t="s">
         <v>225</v>
@@ -6341,59 +6374,59 @@
         <v>716</v>
       </c>
       <c r="B103" t="s">
+        <v>315</v>
+      </c>
+      <c r="C103" t="s">
         <v>717</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
+        <v>225</v>
+      </c>
+      <c r="E103" t="s">
         <v>718</v>
       </c>
-      <c r="D103" t="s">
-        <v>225</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>719</v>
       </c>
-      <c r="F103" t="s">
+      <c r="H103" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>721</v>
+      </c>
+      <c r="B104" t="s">
         <v>722</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
+        <v>263</v>
+      </c>
+      <c r="D104" t="s">
+        <v>225</v>
+      </c>
+      <c r="E104" t="s">
         <v>723</v>
-      </c>
-      <c r="C104" t="s">
-        <v>549</v>
-      </c>
-      <c r="D104" t="s">
-        <v>225</v>
-      </c>
-      <c r="E104" t="s">
-        <v>724</v>
       </c>
       <c r="F104" t="s">
         <v>315</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>725</v>
+      </c>
+      <c r="B105" t="s">
         <v>726</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>727</v>
       </c>
-      <c r="C105" t="s">
-        <v>263</v>
-      </c>
       <c r="D105" t="s">
-        <v>408</v>
+        <v>225</v>
       </c>
       <c r="E105" t="s">
         <v>728</v>
@@ -6413,7 +6446,7 @@
         <v>732</v>
       </c>
       <c r="C106" t="s">
-        <v>263</v>
+        <v>560</v>
       </c>
       <c r="D106" t="s">
         <v>225</v>
@@ -6422,24 +6455,24 @@
         <v>733</v>
       </c>
       <c r="F106" t="s">
+        <v>315</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>735</v>
+      </c>
+      <c r="B107" t="s">
         <v>736</v>
       </c>
-      <c r="B107" t="s">
-        <v>587</v>
-      </c>
       <c r="C107" t="s">
-        <v>313</v>
+        <v>263</v>
       </c>
       <c r="D107" t="s">
-        <v>225</v>
+        <v>413</v>
       </c>
       <c r="E107" t="s">
         <v>737</v>
@@ -6459,16 +6492,16 @@
         <v>741</v>
       </c>
       <c r="C108" t="s">
+        <v>263</v>
+      </c>
+      <c r="D108" t="s">
+        <v>225</v>
+      </c>
+      <c r="E108" t="s">
         <v>742</v>
       </c>
-      <c r="D108" t="s">
-        <v>257</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>743</v>
-      </c>
-      <c r="F108" t="s">
-        <v>315</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>744</v>
@@ -6479,33 +6512,33 @@
         <v>745</v>
       </c>
       <c r="B109" t="s">
+        <v>596</v>
+      </c>
+      <c r="C109" t="s">
+        <v>313</v>
+      </c>
+      <c r="D109" t="s">
+        <v>225</v>
+      </c>
+      <c r="E109" t="s">
         <v>746</v>
       </c>
-      <c r="C109" t="s">
-        <v>303</v>
-      </c>
-      <c r="D109" t="s">
-        <v>225</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>747</v>
       </c>
-      <c r="F109" t="s">
+      <c r="H109" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>749</v>
+      </c>
+      <c r="B110" t="s">
         <v>750</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>751</v>
-      </c>
-      <c r="C110" t="s">
-        <v>351</v>
       </c>
       <c r="D110" t="s">
         <v>257</v>
@@ -6514,7 +6547,7 @@
         <v>752</v>
       </c>
       <c r="F110" t="s">
-        <v>554</v>
+        <v>315</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>753</v>
@@ -6528,7 +6561,7 @@
         <v>755</v>
       </c>
       <c r="C111" t="s">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="D111" t="s">
         <v>225</v>
@@ -6551,30 +6584,30 @@
         <v>760</v>
       </c>
       <c r="C112" t="s">
-        <v>263</v>
+        <v>351</v>
       </c>
       <c r="D112" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E112" t="s">
         <v>761</v>
       </c>
       <c r="F112" t="s">
+        <v>565</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>763</v>
+      </c>
+      <c r="B113" t="s">
         <v>764</v>
       </c>
-      <c r="B113" t="s">
-        <v>587</v>
-      </c>
       <c r="C113" t="s">
-        <v>313</v>
+        <v>263</v>
       </c>
       <c r="D113" t="s">
         <v>225</v>
@@ -6594,148 +6627,148 @@
         <v>768</v>
       </c>
       <c r="B114" t="s">
-        <v>382</v>
+        <v>769</v>
       </c>
       <c r="C114" t="s">
-        <v>383</v>
+        <v>263</v>
       </c>
       <c r="D114" t="s">
         <v>225</v>
       </c>
       <c r="E114" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F114" t="s">
-        <v>227</v>
+        <v>771</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B115" t="s">
-        <v>382</v>
+        <v>596</v>
       </c>
       <c r="C115" t="s">
-        <v>383</v>
+        <v>313</v>
       </c>
       <c r="D115" t="s">
         <v>225</v>
       </c>
       <c r="E115" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="F115" t="s">
-        <v>227</v>
+        <v>775</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B116" t="s">
-        <v>548</v>
+        <v>382</v>
       </c>
       <c r="C116" t="s">
-        <v>549</v>
+        <v>383</v>
       </c>
       <c r="D116" t="s">
         <v>225</v>
       </c>
       <c r="E116" t="s">
-        <v>680</v>
+        <v>778</v>
       </c>
       <c r="F116" t="s">
-        <v>315</v>
+        <v>227</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B117" t="s">
-        <v>290</v>
+        <v>382</v>
       </c>
       <c r="C117" t="s">
-        <v>303</v>
+        <v>383</v>
       </c>
       <c r="D117" t="s">
-        <v>309</v>
+        <v>225</v>
       </c>
       <c r="E117" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="F117" t="s">
-        <v>293</v>
+        <v>227</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="B118" t="s">
-        <v>382</v>
+        <v>559</v>
       </c>
       <c r="C118" t="s">
-        <v>383</v>
+        <v>560</v>
       </c>
       <c r="D118" t="s">
         <v>225</v>
       </c>
       <c r="E118" t="s">
-        <v>780</v>
+        <v>689</v>
       </c>
       <c r="F118" t="s">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B119" t="s">
-        <v>783</v>
+        <v>290</v>
       </c>
       <c r="C119" t="s">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="D119" t="s">
-        <v>225</v>
+        <v>309</v>
       </c>
       <c r="E119" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="F119" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B120" t="s">
-        <v>787</v>
+        <v>382</v>
       </c>
       <c r="C120" t="s">
-        <v>788</v>
+        <v>383</v>
       </c>
       <c r="D120" t="s">
         <v>225</v>
@@ -6744,7 +6777,7 @@
         <v>789</v>
       </c>
       <c r="F120" t="s">
-        <v>315</v>
+        <v>227</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>790</v>
@@ -6758,88 +6791,157 @@
         <v>792</v>
       </c>
       <c r="C121" t="s">
+        <v>263</v>
+      </c>
+      <c r="D121" t="s">
+        <v>225</v>
+      </c>
+      <c r="E121" t="s">
         <v>793</v>
       </c>
-      <c r="D121" t="s">
-        <v>408</v>
-      </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
+        <v>315</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="F121" t="s">
-        <v>293</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="B122" t="s">
-        <v>470</v>
+        <v>795</v>
       </c>
       <c r="C122" t="s">
-        <v>313</v>
+        <v>263</v>
       </c>
       <c r="D122" t="s">
         <v>225</v>
       </c>
       <c r="E122" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="F122" t="s">
         <v>315</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>797</v>
+      </c>
+      <c r="B123" t="s">
+        <v>798</v>
+      </c>
+      <c r="C123" t="s">
         <v>799</v>
       </c>
-      <c r="B123" t="s">
+      <c r="D123" t="s">
+        <v>225</v>
+      </c>
+      <c r="E123" t="s">
         <v>800</v>
       </c>
-      <c r="C123" t="s">
-        <v>250</v>
-      </c>
-      <c r="D123" t="s">
-        <v>225</v>
-      </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
+        <v>315</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>801</v>
-      </c>
-      <c r="F123" t="s">
-        <v>575</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>802</v>
+      </c>
+      <c r="B124" t="s">
         <v>803</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>804</v>
       </c>
-      <c r="C124" t="s">
-        <v>407</v>
-      </c>
       <c r="D124" t="s">
-        <v>225</v>
+        <v>413</v>
       </c>
       <c r="E124" t="s">
         <v>805</v>
       </c>
       <c r="F124" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>806</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>807</v>
+      </c>
+      <c r="B125" t="s">
+        <v>481</v>
+      </c>
+      <c r="C125" t="s">
+        <v>313</v>
+      </c>
+      <c r="D125" t="s">
+        <v>225</v>
+      </c>
+      <c r="E125" t="s">
+        <v>808</v>
+      </c>
+      <c r="F125" t="s">
+        <v>315</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>810</v>
+      </c>
+      <c r="B126" t="s">
+        <v>811</v>
+      </c>
+      <c r="C126" t="s">
+        <v>250</v>
+      </c>
+      <c r="D126" t="s">
+        <v>225</v>
+      </c>
+      <c r="E126" t="s">
+        <v>812</v>
+      </c>
+      <c r="F126" t="s">
+        <v>395</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>814</v>
+      </c>
+      <c r="B127" t="s">
+        <v>815</v>
+      </c>
+      <c r="C127" t="s">
+        <v>412</v>
+      </c>
+      <c r="D127" t="s">
+        <v>225</v>
+      </c>
+      <c r="E127" t="s">
+        <v>816</v>
+      </c>
+      <c r="F127" t="s">
+        <v>315</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -6968,6 +7070,9 @@
     <hyperlink ref="H122" r:id="rId121"/>
     <hyperlink ref="H123" r:id="rId122"/>
     <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
